--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -5114,12 +5114,12 @@
       <c r="C93" s="5" t="inlineStr"/>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -5138,12 +5138,12 @@
       <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs (Ôn lại: 357 ngày)</t>
+          <t>brute force, dfs and similar, graphs (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees (Ôn lại: 843 ngày)</t>
+          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7318,12 +7318,12 @@
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>data structures, sortings (Ôn lại: 356 ngày)</t>
+          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>geometry (Ôn lại: 331 ngày)</t>
+          <t>geometry (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -13863,12 +13863,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -13895,12 +13895,12 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -16707,12 +16707,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr">
@@ -17290,12 +17290,12 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J70" s="22" t="inlineStr">
@@ -18615,12 +18615,12 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J83" s="22" t="inlineStr">
@@ -18640,17 +18640,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2041C</t>
+          <t>2041M</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Selection Sort</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E84" s="20" t="n">
@@ -18658,12 +18658,12 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp</t>
+          <t>binary search, data structures, greedy, two pointers</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -18693,17 +18693,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2041M</t>
+          <t>2041C</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Selection Sort</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="E85" s="20" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, two pointers</t>
+          <t>bitmasks, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J85" s="22" t="inlineStr">
@@ -19092,12 +19092,12 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J92" s="22" t="inlineStr">
@@ -19170,17 +19170,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1991D</t>
+          <t>1991E</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Prime XOR Coloring</t>
+          <t>Coloring Game</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E94" s="20" t="n">
@@ -19188,12 +19188,12 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
+          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1991E</t>
+          <t>1991D</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Coloring Game</t>
+          <t>Prime XOR Coloring</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E95" s="20" t="n">
@@ -19241,22 +19241,22 @@
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
+          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>808 ngày</t>
+          <t>809 ngày</t>
         </is>
       </c>
       <c r="J95" s="22" t="inlineStr">
@@ -19569,12 +19569,12 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J101" s="22" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J114" s="22" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr">
@@ -20890,12 +20890,12 @@
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J126" s="10" t="inlineStr">
@@ -21420,12 +21420,12 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J136" s="10" t="inlineStr">

--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -649,124 +649,124 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-17 (Thứ Bảy)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Thử máy Vòng thi ICPC Miền Nam 2026 (ĐH KHTN TP.HCM)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gyms</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ICPC Miền Nam 2026 - Practice Session</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>ICPC Team</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>THỬ MÁY</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18 (Chủ Nhật)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CHÍNH THỨC THI ICPC MIỀN NAM 2026 (5 GIỜ)</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gyms</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>ICPC Southern Vietnam Regional Contest 2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>ICPC Team</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>OFFICIAL CONTEST</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>2026-10-19 (Thứ Hai)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Ôn tập Lý thuyết &amp; Re-solve bài cũ: DSU Tree &amp; Small to Large</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/contest/1416/problem/D</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 1416D - DSU Tree</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Re-solve bài cũ</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20 (Thứ Ba)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Luyện tập Ladder 16: Graph &amp; Shortest Paths</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/contest/295/problem/B</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 295B - Greg and Graph (Floyd-Warshall trick)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Ladder 16 Re-solve</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-21 (Thứ Tư)</t>
-        </is>
-      </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mini-Contest #1 (2.5h)</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/contest/1996</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Codeforces Round 962 (Div. 3/2)</t>
+          <t>Upsolving đề ICPC Miền Nam &amp; Phân tích lỗi kỹ thuật phòng thi</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gyms</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Upsolve ICPC Miền Nam</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1200-1800</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Mini Mock Test</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Upsolving</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -775,32 +775,32 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 (Thứ Năm)</t>
+          <t>2026-10-20 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ: Mo on Tree &amp; Rerooting</t>
+          <t>Re-solve bài cũ: DSU Tree &amp; Small to Large</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/375/D</t>
+          <t>https://codeforces.com/contest/1416/problem/D</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 375D - Mo on tree</t>
+          <t>Codeforces 1416D - DSU Tree</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -817,37 +817,37 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 (Thứ Sáu)</t>
+          <t>2026-10-21 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Thực hành Ladder 16: DFS/BFS &amp; Constructive</t>
+          <t>Ladder 16 Re-solve: Graph &amp; Shortest Paths (Floyd trick)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/217/A</t>
+          <t>https://codeforces.com/contest/295/problem/B</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 217A - Ice Skating</t>
+          <t>Codeforces 295B - Greg and Graph</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Ladder 16</t>
+          <t>Ladder 16 Re-solve</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -859,37 +859,37 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 (Thứ Bảy)</t>
+          <t>2026-10-22 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Upsolving &amp; Tối ưu hóa Code Template (Tree/Graph)</t>
+          <t>Re-solve bài cũ: Mo on Tree &amp; Rerooting</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/diffgraph</t>
+          <t>https://codeforces.com/problemset/problem/375/D</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>LQDOJ diffgraph - Small to large, reroot</t>
+          <t>Codeforces 375D - Mo on tree</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>VNOI/LQDOJ Practice</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -899,42 +899,42 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-25 (Chủ Nhật)</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 (Thứ Sáu)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tuần 1: Củng cố Cây (Tree), DSU nâng cao &amp; Đường đi ngắn nhất (Shortest Path)</t>
+          <t>Tuần 1: VÒNG THI ICPC MIỀN NAM 2026 &amp; Củng cố Cây (Tree), DSU</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>MOCK TEST 1: ICPC Regional Simulation 5 Giờ (Team Contest #1)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/gym/104021</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>2022-2023 ICPC Asia Yokohama Regional</t>
+          <t>Rà soát Template &amp; Chuẩn bị chiến thuật Vòng Miền Trung</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/problemset/problem/217/A</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Codeforces 217A - Ice Skating</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>ICPC Team</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>FULL MOCK TEST</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Review Template</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -943,37 +943,37 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 (Thứ Hai)</t>
+          <t>2026-10-24 (Thứ Bảy)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Ôn tập SOS DP &amp; Bitmask: Re-solve các bài kinh điển</t>
+          <t>Thử máy Vòng thi ICPC Miền Trung 2026 (ĐH Khoa học - ĐH Huế)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://cses.fi/problemset/task/1654</t>
+          <t>https://codeforces.com/gyms</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>CSES 1654 - SOS DP</t>
+          <t>ICPC Miền Trung 2026 - Practice Session</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>ICPC Team</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Re-solve</t>
+          <t>THỬ MÁY</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -983,42 +983,42 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 (Thứ Ba)</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-25 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ: SOS DP &amp; Bao hàm loại trừ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/449/D</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 449D - Jzzhu and Numbers</t>
+          <t>CHÍNH THỨC THI ICPC MIỀN TRUNG 2026 (5 GIỜ)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gyms</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>ICPC Central Vietnam Regional Contest 2026</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Re-solve bài cũ</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+          <t>ICPC Team</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>OFFICIAL CONTEST</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -1027,37 +1027,37 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 (Thứ Tư)</t>
+          <t>2026-10-26 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mock Contest #2 (3h)</t>
+          <t>Upsolve đề Miền Trung &amp; Củng cố SOS DP</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/1987</t>
+          <t>https://cses.fi/problemset/task/1654</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Codeforces Round 955 (Div. 2/1)</t>
+          <t>CSES 1654 - SOS DP</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>1500-2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>OLP Mock Test</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1069,27 +1069,27 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 (Thứ Năm)</t>
+          <t>2026-10-27 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Convex Hull Trick &amp; Li Chao Tree / Alien's Trick</t>
+          <t>Re-solve bài cũ: SOS DP &amp; Bao hàm loại trừ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1715/E</t>
+          <t>https://codeforces.com/problemset/problem/449/D</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 1715E - Long Way Home (Dijkstra + CHT)</t>
+          <t>Codeforces 449D - Jzzhu and Numbers</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1109,42 +1109,42 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30 (Thứ Sáu)</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ladder 16: DP &amp; Strings (KMP + DP)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/346/B</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 346B - Lucky Common Subsequence</t>
+          <t>Kiểm tra cá nhân OLP Mini-Mock Contest (2.5h - CF Div.2)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/contest/1987</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Codeforces Round 955 (Div. 2/1)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Ladder 16 Re-solve</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+          <t>1500-2200</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>OLP Mini Test</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -1153,37 +1153,37 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31 (Thứ Bảy)</t>
+          <t>2026-10-29 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Upsolve các bài DP chưa hoàn thành &amp; Team Strategy</t>
+          <t>Convex Hull Trick &amp; Li Chao Tree / Alien's Trick</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/voi21_or</t>
+          <t>https://codeforces.com/problemset/problem/1715/E</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>VOI 2021 OR - SOS DP</t>
+          <t>Codeforces 1715E - Long Way Home (Dijkstra + CHT)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>VOI</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>VOI Practice</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1193,42 +1193,42 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-01 (Chủ Nhật)</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 (Thứ Sáu)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Tuần 2: Dynamic Programming nâng cao (SOS DP, CHT, Bitmask, Tree DP)</t>
+          <t>Tuần 2: VÒNG THI ICPC MIỀN TRUNG 2026 &amp; Quy hoạch động nâng cao (SOS DP, CHT)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MOCK TEST 2: ICPC Regional Simulation 5 Giờ (Team Contest #2)</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/gym/104114</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>2022 ICPC Asia Can Tho Regional Contest</t>
+          <t>Ladder 16 Re-solve: KMP + DP</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/problemset/problem/346/B</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Codeforces 346B - Lucky Common Subsequence</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>ICPC Team</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>FULL MOCK TEST</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Ladder 16 Re-solve</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -1237,12 +1237,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-02 (Thứ Hai)</t>
+          <t>2026-10-31 (Thứ Bảy)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1279,37 +1279,37 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03 (Thứ Ba)</t>
+          <t>2026-11-01 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Ladder 16: Segment Tree &amp; Modulo Trick</t>
+          <t>MOCK TEST QUỐC GIA 5H: Giả lập ICPC Vietnam National 2023</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/438/D</t>
+          <t>https://codeforces.com/gym/104725</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 438D - The Child and Sequence</t>
+          <t>2023 ICPC Vietnam National Contest</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>ICPC Team</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Ladder 16 Re-solve</t>
+          <t>FULL MOCK TEST</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1321,37 +1321,37 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04 (Thứ Tư)</t>
+          <t>2026-11-02 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mock Contest #3 (3.5h - CTDL &amp; DP)</t>
+          <t>Upsolve đề Mock Test Quốc Gia &amp; Tối ưu hóa phân chia bài</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/coci1920_o_paint</t>
+          <t>https://codeforces.com/problemset/problem/438/D</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>COCI 1920 Paint - Chia căn lớn bé &amp; DSU</t>
+          <t>Codeforces 438D - The Child and Sequence (SegTree Modulo)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>OLP Mock Test</t>
+          <t>Upsolving</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1363,37 +1363,37 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05 (Thứ Năm)</t>
+          <t>2026-11-03 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Persistent Segment Tree &amp; Treap cơ bản</t>
+          <t>Kiểm tra và in ấn Team Notebook bản chuẩn cho kỳ thi Quốc Gia</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/986/problem/E</t>
+          <t>https://codeforces.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 986E - Prince's Problem (Tree, DS, Math)</t>
+          <t>ICPC Team Notebook - 25 Trang</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>Teamwork</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1405,37 +1405,37 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06 (Thứ Sáu)</t>
+          <t>2026-11-04 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ladder 16: Data Structures &amp; Hashing</t>
+          <t>Rà soát bẫy tràn số (MOD, 64-bit, fast I/O) &amp; Viết test generator</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/126/B</t>
+          <t>https://codeforces.com/contest/786/problem/B</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 126B - Password</t>
+          <t>Codeforces 786B - Segment Tree trên đồ thị</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Ladder 16 Re-solve</t>
+          <t>Stress Test Lab</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -1447,37 +1447,37 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07 (Thứ Bảy)</t>
+          <t>2026-11-05 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Review Template SegTree Lazy &amp; Fenwick 2D</t>
+          <t>Chiến thuật tâm lý thi đấu 3 người 1 máy vòng Quốc Gia</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/segtree_itteq1</t>
+          <t>https://codeforces.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>VNOI ITTEQ1 - Segment Tree nâng cao</t>
+          <t>Họp chiến thuật Team ICPC</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Review Template</t>
+          <t>Team Meeting</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1487,81 +1487,81 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-08 (Chủ Nhật)</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06 (Thứ Sáu)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Tuần 3: Cấu trúc dữ liệu nâng cao &amp; Chia căn (Mo, Sqrt Decomposition, SegTree)</t>
+          <t>Tuần 3: TỔNG LỰC CHUẨN BỊ CHO KỲ THI ICPC QUỐC GIA 2026</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>MOCK TEST 3: ICPC Regional Simulation 5 Giờ (Team Contest #3)</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/gym/103449</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>2021-2022 ICPC Asia Hanoi Regional Contest</t>
+          <t>Thư giãn, ngủ đủ giấc, chuẩn bị tài khoản và máy thi</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Nghỉ ngơi nạp năng lượng trước Vòng Quốc Gia</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>ICPC Team</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>FULL MOCK TEST</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Rest &amp; Recharge</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09 (Thứ Hai)</t>
+          <t>2026-11-07 (Thứ Bảy)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Bao hàm loại trừ &amp; Lucas Theorem: Re-solve bài cũ</t>
+          <t>Thử máy Kỳ thi ICPC Quốc gia 2026 tại điểm thi tập trung</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/1043/problem/F</t>
+          <t>https://codeforces.com/gyms</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 1043F - Make It One (Bao hàm)</t>
+          <t>ICPC Vietnam National 2026 - Practice Session</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>ICPC Team</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ</t>
+          <t>THỬ MÁY</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1573,37 +1573,37 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-10 (Thứ Ba)</t>
+          <t>2026-11-08 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Toán chia kẹo Euler &amp; Nghịch đảo modulo</t>
+          <t>CHÍNH THỨC THI ICPC QUỐC GIA 2026 (VIETNAM NATIONAL - 5 GIỜ)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/c11tct</t>
+          <t>https://codeforces.com/gyms</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>VNOI c11tct - Chia kẹo, Lucas theory</t>
+          <t>2026 ICPC Vietnam National Contest</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>ICPC Team</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>VNOI Math</t>
+          <t>OFFICIAL CONTEST</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -1615,37 +1615,37 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-11 (Thứ Tư)</t>
+          <t>2026-11-09 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mock Contest #4 (3h - Toán &amp; Tổ hợp)</t>
+          <t>Tổng kết kết quả vòng Quốc gia &amp; Xác định slot dự Regional Đà Nẵng</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/1974</t>
+          <t>https://olp.vn</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Codeforces Round 946</t>
+          <t>Bảng điểm ICPC Quốc Gia 2026</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Div.3/2</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>OLP Mock Test</t>
+          <t>Debrief</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -1657,32 +1657,32 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-11-12 (Thứ Năm)</t>
+          <t>2026-11-10 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hình học Sweepline &amp; Convex Hull: Re-solve bài cũ</t>
+          <t>Upsolving toàn bộ các bài trong tầm với đề ICPC Quốc Gia 2026</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/529/problem/C</t>
+          <t>https://codeforces.com/contest/1043/problem/F</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 529C - Sweepline (Rooks Defender)</t>
+          <t>Codeforces 1043F - Make It One (Bao hàm loại trừ)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1699,27 +1699,27 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-11-13 (Thứ Sáu)</t>
+          <t>2026-11-11 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Hình học tính toán &amp; Bao lồi (Monotone Chain)</t>
+          <t>Khởi động giai đoạn 2: Ôn luyện cá nhân Olympic Tin học SV</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/cavli</t>
+          <t>https://oj.vnoi.info/problem/c11tct</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>VNOI cavli - Hình học, Bao lồi</t>
+          <t>VNOI c11tct - Chia kẹo Euler &amp; Lucas</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Geometry</t>
+          <t>OLP Practice</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1741,82 +1741,82 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-11-14 (Thứ Bảy)</t>
+          <t>2026-11-12 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>Toán học &amp; Tổ hợp: Re-solve các bài toán chia kẹo, nghịch đảo</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://oj.vnoi.info/problem/fc090_divcan</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>VNOI fc090_divcan - Bao hàm, Lucas</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Re-solve</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-13 (Thứ Sáu)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 4: KỲ THI ICPC QUỐC GIA 2026 (08-09/11) &amp; BƯỚC NGOẶT CHUYỂN GIAO</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
           <t>Ladder 16: Math &amp; Number Theory</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>https://codeforces.com/problemset/problem/354/C</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Codeforces 354C - Vasya and Beautiful Arrays</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Ladder 16 Re-solve</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-15 (Chủ Nhật)</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 4: Toán học, Tổ hợp, Nghịch đảo Modulo &amp; Hình học Sweepline</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>MOCK TEST 4: ICPC Regional Simulation 5 Giờ (Team Contest #4)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/gym/104639</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>2023-2024 ICPC Asia Hue Regional Contest</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>ICPC Team</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>FULL MOCK TEST</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -1825,37 +1825,37 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16 (Thứ Hai)</t>
+          <t>2026-11-14 (Thứ Bảy)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>KMP, Z-function &amp; Hash 2D: Re-solve bài cũ</t>
+          <t>Hình học tính toán: Bao lồi (Monotone Chain / Graham Scan)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/432/D</t>
+          <t>https://oj.vnoi.info/problem/cavli</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 432D - Prefixes and Suffixes</t>
+          <t>VNOI cavli - Hình học, Bao lồi</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Ladder 16 Re-solve</t>
+          <t>Geometry</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -1867,37 +1867,37 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-11-17 (Thứ Ba)</t>
+          <t>2026-11-15 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Aho-Corasick &amp; DP trên Trie</t>
+          <t>MOCK TEST OLP #1: Đề thi Siêu Cúp / Chuyên Tin các năm (3.5 giờ)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://lqdoj.edu.vn/problem/lqdoj2022r4ugpalind</t>
+          <t>https://cms.ioi-jp.org/joi2023-sp1-open</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>LQDOJ ugpalind - DP + Aho-Corasick</t>
+          <t>JOI Spring Camp 2023 Contest 1</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>LQDOJ String</t>
+          <t>OLP Mock Test</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -1909,37 +1909,37 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-11-18 (Thứ Tư)</t>
+          <t>2026-11-16 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mock Contest #5 (3.5h - Đề Siêu Cúp / Chuyên Tin)</t>
+          <t>Sweepline quét tọa độ X kết hợp Segment Tree</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://cms.ioi-jp.org/joi2023-sp1-open</t>
+          <t>https://codeforces.com/contest/529/problem/C</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>JOI Spring Camp 2023 Contest 1</t>
+          <t>Codeforces 529C - Sweepline (Rooks Defender)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>OLP Mock Test</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -1951,32 +1951,32 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-11-19 (Thứ Năm)</t>
+          <t>2026-11-17 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Luồng cực đại (Dinic) &amp; Cặp ghép cực đại</t>
+          <t>Persistent Segment Tree &amp; Treap: Re-solve bài cũ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/944/problem/F</t>
+          <t>https://codeforces.com/contest/986/problem/E</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 944F - CTDL, Game</t>
+          <t>Codeforces 986E - Prince's Problem (Tree, DS, Math)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20 (Thứ Sáu)</t>
+          <t>2026-11-18 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Game Theory: Nim, Sprague-Grundy &amp; Nhận xét Adhoc</t>
+          <t>Kỹ thuật Chia căn lớn bé &amp; DSU</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/2181/problem/F</t>
+          <t>https://oj.vnoi.info/problem/coci1920_o_paint</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 2181F - Fragmented Nim</t>
+          <t>COCI 1920 Paint - Chia căn lớn bé &amp; DSU</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -2035,17 +2035,17 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-11-21 (Thứ Bảy)</t>
+          <t>2026-11-19 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Ladder 16: KMP String Differencing</t>
+          <t>Ladder 16: KMP Differencing</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2077,37 +2077,37 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-11-22 (Chủ Nhật)</t>
+          <t>2026-11-20 (Thứ Sáu)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Tuần 5: Thuật toán Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
+          <t>Tuần 5: Chuyên sâu Olympic: Hình học Sweepline, Bao lồi &amp; CTDL Nâng cao</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>MOCK TEST 5: ICPC Vietnam National Simulation 5 Giờ (Team Contest #5)</t>
+          <t>Review Template SegTree Lazy &amp; Fenwick 2D</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/gym/104725</t>
+          <t>https://oj.vnoi.info/problem/segtree_itteq1</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2023 ICPC Vietnam National Contest</t>
+          <t>VNOI ITTEQ1 - Segment Tree nâng cao</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>ICPC Team</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>FULL MOCK TEST</t>
+          <t>Review Template</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -2119,37 +2119,37 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23 (Thứ Hai)</t>
+          <t>2026-11-21 (Thứ Bảy)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Upsolving bài khó Mock Test 5 &amp; Phân tích bug phòng thi</t>
+          <t>KMP, Z-function &amp; Hash 2D: Re-solve bài cũ</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/1442/problem/C</t>
+          <t>https://codeforces.com/problemset/problem/432/D</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 1442C - Graph, Shortest Path</t>
+          <t>Codeforces 432D - Prefixes and Suffixes</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ</t>
+          <t>Ladder 16 Re-solve</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -2159,42 +2159,42 @@
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-24 (Thứ Ba)</t>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-22 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Re-solve bài cũ: DSU on Tree / Small to large</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/570/D</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 570D - Tree Requests</t>
+          <t>MOCK TEST REGIONAL #4: 2023-2024 ICPC Asia Hue Regional Contest (5h)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gym/104639</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>2023-2024 ICPC Asia Hue Regional Contest</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Ladder 16 Re-solve</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+          <t>ICPC Team</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>FULL MOCK TEST</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -2203,37 +2203,37 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-11-25 (Thứ Tư)</t>
+          <t>2026-11-23 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra cá nhân OLP Mock Contest #6 (3h - Đề Olympic các năm)</t>
+          <t>Aho-Corasick &amp; DP trên Trie</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://oj.vnoi.info/problem/voi21_rmat</t>
+          <t>https://lqdoj.edu.vn/problem/lqdoj2022r4ugpalind</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>VOI 2021 RMAT - Observation &amp; Matrix</t>
+          <t>LQDOJ ugpalind - DP + Aho-Corasick</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>VOI</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>OLP Mock Test</t>
+          <t>LQDOJ String</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -2245,27 +2245,27 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-11-26 (Thứ Năm)</t>
+          <t>2026-11-24 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra và hoàn thiện ICPC Team Notebook (Codeforces Template)</t>
+          <t>Luồng cực đại (Dinic) &amp; Cặp ghép hai phía</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/1697/problem/E</t>
+          <t>https://codeforces.com/contest/944/problem/F</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 1697E - Graph, DP, Tổ hợp</t>
+          <t>Codeforces 944F - CTDL, Game</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2287,37 +2287,37 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-11-27 (Thứ Sáu)</t>
+          <t>2026-11-25 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Thực hành Stress Test (Viết script sinh test ngẫu nhiên đối chiếu)</t>
+          <t>Game Theory: Nim, Sprague-Grundy &amp; Nhận xét Adhoc</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://dmoj.ca/problem/coci06c1p6</t>
+          <t>https://codeforces.com/contest/2181/problem/F</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>COCI 06 c1p6 - Hash 2D</t>
+          <t>Codeforces 2181F - Fragmented Nim</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Stress Test Lab</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -2329,27 +2329,27 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-11-28 (Thứ Bảy)</t>
+          <t>2026-11-26 (Thứ Năm)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Review toàn bộ các Trick lỏ &amp; bẫy tràn số (Overflow, MOD, 1LL&lt;&lt;x)</t>
+          <t>DSU on tree (Small to large) kết hợp Bitmask</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/786/problem/B</t>
+          <t>https://codeforces.com/problemset/problem/570/D</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 786B - Dijkstra đoạn</t>
+          <t>Codeforces 570D - Tree Requests</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Trick lỏ</t>
+          <t>Ladder 16 Re-solve</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -2371,82 +2371,82 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-11-29 (Chủ Nhật)</t>
+          <t>2026-11-27 (Thứ Sáu)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Tuần 6: Tổng lực Luyện đề, Chiến thuật Team &amp; Stress Testing</t>
+          <t>Tuần 6: Xâu ký tự (Strings), Luồng cực đại (Flow) &amp; Game Theory</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MOCK TEST 6: FINAL FULL ICPC SIMULATION 5 GIỜ</t>
+          <t>Kiểm tra tiến độ 137 bài khó đã re-solve được bao nhiêu bài</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/gym/103960</t>
+          <t>https://codeforces.com/contest/1442/problem/C</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2022-2023 ICPC Brazil Subregional / Asia Archive</t>
+          <t>Codeforces 1442C - Graph, Shortest Path</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Re-solve bài cũ</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-28 (Thứ Bảy)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>FINAL MOCK TEST: 2022-2023 ICPC Asia Yokohama Regional (5 Giờ)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/gym/104021</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>2022-2023 ICPC Asia Yokohama Regional</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>ICPC Team</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>FINAL MOCK TEST</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30 (Thứ Hai)</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Re-solve nhẹ nhàng: Ladder 16 các bài trung bình (Lấy cảm giác tay)</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/476/B</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Codeforces 476B - Dreamoon and WiFi</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Ladder 16</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -2455,37 +2455,37 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-12-01 (Thứ Ba)</t>
+          <t>2026-11-29 (Chủ Nhật)</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Rà soát lại danh sách 137 bài khó đã ôn tập</t>
+          <t>MOCK TEST OLP #2: Đề Olympic Tin học Sinh viên Toàn quốc (3.5 Giờ)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com/contest/2181/problem/D</t>
+          <t>https://oj.vnoi.info/problem/voi21_rmat</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Codeforces 2181D - Doorway (BS + DS)</t>
+          <t>VOI 2021 RMAT - Observation &amp; Matrix</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>VOI</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Re-solve nhẹ</t>
+          <t>OLP Mock Test</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -2497,37 +2497,37 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-12-02 (Thứ Tư)</t>
+          <t>2026-11-30 (Thứ Hai)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Kiểm tra Template Notebook, máy chấm, compiler flags (-O2, -fsanitize)</t>
+          <t>Upsolve bài khó Mock Test &amp; Đóng gói toàn bộ code mẫu</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://codeforces.com</t>
+          <t>https://codeforces.com/contest/1697/problem/E</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Chuẩn bị môi trường thi &amp; template in ấn</t>
+          <t>Codeforces 1697E - Graph, DP, Tổ hợp</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Re-solve bài cũ</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -2539,17 +2539,17 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-12-03 (Thứ Năm)</t>
+          <t>2026-12-01 (Thứ Ba)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Chiến thuật tâm lý: Phân bổ thời gian, nhận diện bài bẫy</t>
+          <t>In ấn Team Notebook bản cứng (25 trang chuẩn ICPC quốc tế)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Họp chiến thuật team ICPC</t>
+          <t>In ấn Team Notebook</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Team Meeting</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -2581,17 +2581,17 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-12-04 (Thứ Sáu)</t>
+          <t>2026-12-02 (Thứ Tư)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi, ngủ đủ giấc, chuẩn bị thẻ sinh viên &amp; CCCD</t>
+          <t>Kiểm tra compiler flags (-O2, -fsanitize=undefined) &amp; máy chấm</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2601,104 +2601,398 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi chuẩn bị cho ngày thi</t>
+          <t>Kiểm tra môi trường thi</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Rest &amp; Recharge</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>Hoàn thành</t>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>2026-12-03 (Thứ Năm)</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Họp chiến thuật team 3 người 1 máy lần cuối trước khi bay</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Họp chiến thuật Team ICPC</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-04 (Thứ Sáu)</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 7: Tổng duyệt cuối cùng &amp; Chuẩn bị lên đường đi Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Nghỉ ngơi, chuẩn bị hành lý, giấy tờ tùy thân và vé đi Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Nghỉ ngơi và chuẩn bị lên đường</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Rest &amp; Recharge</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>2026-12-05 (Thứ Bảy)</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>NGÀY THI OLYMPIC TIN HỌC SINH VIÊN (CÁ NHÂN)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Di chuyển đến TP. Đà Nẵng, nhận phòng &amp; ổn định nơi lưu trú</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>https://olp.vn</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Olympic Tin học Sinh viên Toàn quốc</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Có mặt tại Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Check-in</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-06 (Chủ Nhật)</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Tham quan Trường ĐH CNTT và Truyền thông Việt - Hàn (VKU Đà Nẵng)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>https://olp.vn</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Thăm quan địa điểm thi VKU Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Site Visit</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Venue Tour</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-07 (Thứ Hai)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Gõ code nhẹ nhàng vài bài cơ bản lấy cảm giác phím mượt mà</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>https://codeforces.com/problemset/problem/476/B</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Codeforces 476B - Dreamoon and WiFi</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Warm-up</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-08 (Thứ Ba)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>ĐĂNG KÝ THAM GIA OLP &amp; ICPC ASIA DANANG TẠI VKU; CHUNG KẾT OLYMPIC AI</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>https://olp.vn</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Đăng ký OLP'26 &amp; ICPC Asia Danang (08/12/2026)</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>OFFICIAL EVENT</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-09 (Thứ Tư)</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>CHÍNH THỨC THI OLYMPIC TIN HỌC SINH VIÊN (OLP'26) - KHỐI CHUYÊN TIN &amp; SIÊU CÚP</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://olp.vn</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Kỳ thi Cá nhân Olympic Tin học SV 2026 (09/12/2026)</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>CONTEST</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>OFFICIAL CONTEST</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>Đến giờ G!</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>2026-12-06 (Chủ Nhật)</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Tuần 7: Tapering, Thư giãn trí não &amp; Rà soát lần cuối trước giờ G</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>NGÀY THI ICPC REGIONAL (TEAM 3 NGƯỜI / 5 GIỜ)</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10 (Thứ Năm)</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>KHAI MẠC ICPC ASIA DANANG 2026; THỬ MÁY (PRACTICE SESSION 2H) &amp; NỘP NOTEBOOK</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>https://olp.vn</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Khai mạc &amp; Thử máy ICPC Asia Danang (10/12/2026)</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>OFFICIAL EVENT</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Đến giờ G!</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-11 (Thứ Sáu)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Tuần 8: VÒNG CHUNG KẾT TOÀN QUỐC OLP'26 &amp; ICPC ASIA DANANG 2026 (TẠI VKU)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>CHÍNH THỨC THI LẬP TRÌNH QUỐC TẾ ICPC ASIA DANANG 2026 (5 TIẾNG: 08:00 - 13:00)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>https://icpc.global</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>ICPC Asia Regional Contest</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Chính thức thi ICPC Asia Danang 2026 (11/12/2026)</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>CONTEST</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>OFFICIAL CONTEST</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Đến giờ G!</t>
         </is>
@@ -5114,12 +5408,12 @@
       <c r="C93" s="5" t="inlineStr"/>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -5138,12 +5432,12 @@
       <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -5167,7 +5461,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs (Ôn lại: 358 ngày)</t>
+          <t>brute force, dfs and similar, graphs (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -5311,7 +5605,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -5952,7 +6246,7 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
+          <t>dfs and similar, graphs, trees (Ôn lại: 843 ngày)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -7235,7 +7529,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7318,12 +7612,12 @@
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7350,12 +7644,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -7615,7 +7909,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -7703,7 +7997,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 357 ngày)</t>
+          <t>greedy, math (Ôn lại: 356 ngày)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -7791,7 +8085,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -8328,7 +8622,7 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -8428,7 +8722,7 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -8788,7 +9082,7 @@
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -10095,7 +10389,7 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
+          <t>data structures, sortings (Ôn lại: 356 ngày)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -10283,7 +10577,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -12031,7 +12325,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>geometry (Ôn lại: 332 ngày)</t>
+          <t>geometry (Ôn lại: 331 ngày)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -12408,7 +12702,7 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -13068,7 +13362,7 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -13148,7 +13442,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 357 ngày)</t>
+          <t>greedy, math (Ôn lại: 356 ngày)</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -13168,7 +13462,7 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -13755,7 +14049,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -13863,12 +14157,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -13895,12 +14189,12 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -14028,7 +14322,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -16707,12 +17001,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>330 ngày</t>
+          <t>329 ngày</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr">
@@ -17290,12 +17584,12 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr">
@@ -17926,12 +18220,12 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>356 ngày</t>
         </is>
       </c>
       <c r="J70" s="22" t="inlineStr">
@@ -18615,12 +18909,12 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>332 ngày</t>
+          <t>331 ngày</t>
         </is>
       </c>
       <c r="J83" s="22" t="inlineStr">
@@ -18640,17 +18934,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2041M</t>
+          <t>2041C</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Selection Sort</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="E84" s="20" t="n">
@@ -18658,12 +18952,12 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, two pointers</t>
+          <t>bitmasks, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -18693,17 +18987,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2041C</t>
+          <t>2041M</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Selection Sort</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E85" s="20" t="n">
@@ -18711,22 +19005,22 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp</t>
+          <t>binary search, data structures, greedy, two pointers</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>330 ngày</t>
+          <t>329 ngày</t>
         </is>
       </c>
       <c r="J85" s="22" t="inlineStr">
@@ -19092,12 +19386,12 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>844 ngày</t>
+          <t>843 ngày</t>
         </is>
       </c>
       <c r="J92" s="22" t="inlineStr">
@@ -19170,17 +19464,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1991E</t>
+          <t>1991D</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Coloring Game</t>
+          <t>Prime XOR Coloring</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E94" s="20" t="n">
@@ -19188,12 +19482,12 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
+          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -19223,17 +19517,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1991D</t>
+          <t>1991E</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Prime XOR Coloring</t>
+          <t>Coloring Game</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E95" s="20" t="n">
@@ -19241,22 +19535,22 @@
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
+          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>809 ngày</t>
+          <t>808 ngày</t>
         </is>
       </c>
       <c r="J95" s="22" t="inlineStr">
@@ -19569,12 +19863,12 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>356 ngày</t>
         </is>
       </c>
       <c r="J101" s="22" t="inlineStr">
@@ -20258,12 +20552,12 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J114" s="22" t="inlineStr">
@@ -20625,12 +20919,12 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>844 ngày</t>
+          <t>843 ngày</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr">
@@ -20890,12 +21184,12 @@
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>356 ngày</t>
         </is>
       </c>
       <c r="J126" s="10" t="inlineStr">
@@ -21420,12 +21714,12 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>332 ngày</t>
+          <t>331 ngày</t>
         </is>
       </c>
       <c r="J136" s="10" t="inlineStr">

--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -5408,12 +5408,12 @@
       <c r="C93" s="5" t="inlineStr"/>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -5432,12 +5432,12 @@
       <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs (Ôn lại: 357 ngày)</t>
+          <t>brute force, dfs and similar, graphs (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees (Ôn lại: 843 ngày)</t>
+          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7612,12 +7612,12 @@
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>data structures, sortings (Ôn lại: 356 ngày)</t>
+          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>geometry (Ôn lại: 331 ngày)</t>
+          <t>geometry (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -14157,12 +14157,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -14189,12 +14189,12 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr">
@@ -18220,12 +18220,12 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J70" s="22" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J83" s="22" t="inlineStr">
@@ -18934,17 +18934,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2041C</t>
+          <t>2041M</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Selection Sort</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E84" s="20" t="n">
@@ -18952,12 +18952,12 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp</t>
+          <t>binary search, data structures, greedy, two pointers</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -18987,17 +18987,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2041M</t>
+          <t>2041C</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Selection Sort</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="E85" s="20" t="n">
@@ -19005,22 +19005,22 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, two pointers</t>
+          <t>bitmasks, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J85" s="22" t="inlineStr">
@@ -19386,12 +19386,12 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J92" s="22" t="inlineStr">
@@ -19464,17 +19464,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1991D</t>
+          <t>1991E</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Prime XOR Coloring</t>
+          <t>Coloring Game</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E94" s="20" t="n">
@@ -19482,12 +19482,12 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
+          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -19517,17 +19517,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1991E</t>
+          <t>1991D</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Coloring Game</t>
+          <t>Prime XOR Coloring</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E95" s="20" t="n">
@@ -19535,22 +19535,22 @@
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
+          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>808 ngày</t>
+          <t>809 ngày</t>
         </is>
       </c>
       <c r="J95" s="22" t="inlineStr">
@@ -19863,12 +19863,12 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J101" s="22" t="inlineStr">
@@ -20552,12 +20552,12 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J114" s="22" t="inlineStr">
@@ -20919,12 +20919,12 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr">
@@ -21184,12 +21184,12 @@
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J126" s="10" t="inlineStr">
@@ -21714,12 +21714,12 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J136" s="10" t="inlineStr">

--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -13593,12 +13593,12 @@
       <c r="C93" s="17" t="inlineStr"/>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr">
@@ -13617,12 +13617,12 @@
       <c r="C94" s="17" t="inlineStr"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs (Ôn lại: 357 ngày)</t>
+          <t>brute force, dfs and similar, graphs (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees (Ôn lại: 843 ngày)</t>
+          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C136" s="17" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -15797,12 +15797,12 @@
       <c r="C47" s="17" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -15829,12 +15829,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>data structures, sortings (Ôn lại: 356 ngày)</t>
+          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 329 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>geometry (Ôn lại: 331 ngày)</t>
+          <t>geometry (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 329 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>greedy, math, number theory (Ôn lại: 843 ngày)</t>
+          <t>greedy, math, number theory (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>greedy, math (Ôn lại: 356 ngày)</t>
+          <t>greedy, math (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>graphs, greedy, math (Ôn lại: 331 ngày)</t>
+          <t>graphs, greedy, math (Ôn lại: 332 ngày)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 357 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -22342,12 +22342,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
+          <t>constructive algorithms, dfs and similar, games (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -22374,12 +22374,12 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games (Ôn lại: 808 ngày)</t>
+          <t>bitmasks, constructive algorithms, graphs (Ôn lại: 809 ngày)</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 356 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
@@ -25186,12 +25186,12 @@
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -25769,12 +25769,12 @@
       </c>
       <c r="H58" s="21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -26405,12 +26405,12 @@
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -27094,12 +27094,12 @@
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
@@ -27119,17 +27119,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2041C</t>
+          <t>2041M</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Selection Sort</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E84" s="20" t="n">
@@ -27137,12 +27137,12 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp</t>
+          <t>binary search, data structures, greedy, two pointers</t>
         </is>
       </c>
       <c r="H84" s="21" t="inlineStr">
@@ -27172,17 +27172,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2041M</t>
+          <t>2041C</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Selection Sort</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="E85" s="20" t="n">
@@ -27190,22 +27190,22 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, two pointers</t>
+          <t>bitmasks, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H85" s="21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>329 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
@@ -27571,12 +27571,12 @@
       </c>
       <c r="H92" s="21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -27649,17 +27649,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1991D</t>
+          <t>1991E</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Prime XOR Coloring</t>
+          <t>Coloring Game</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E94" s="20" t="n">
@@ -27667,12 +27667,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
+          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -27702,17 +27702,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1991E</t>
+          <t>1991D</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Coloring Game</t>
+          <t>Prime XOR Coloring</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E95" s="20" t="n">
@@ -27720,22 +27720,22 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
+          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H95" s="21" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>808 ngày</t>
+          <t>809 ngày</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
@@ -28048,12 +28048,12 @@
       </c>
       <c r="H101" s="21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="H114" s="21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -29104,12 +29104,12 @@
       </c>
       <c r="H121" s="21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>843 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
@@ -29369,12 +29369,12 @@
       </c>
       <c r="H126" s="21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>356 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr">
@@ -29899,12 +29899,12 @@
       </c>
       <c r="H136" s="21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr">
         <is>
-          <t>331 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J136" s="11" t="inlineStr">

--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -32088,7 +32088,7 @@
           <t>Andrey and Problem</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>http://codeforces.com/problemset/problem/442/B</t>
         </is>
@@ -32101,21 +32101,27 @@
       <c r="E45" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="21" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+      <c r="F45" s="21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>greedy, math, probabilities</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành gần đây</t>
         </is>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
-          <t>Chưa nộp</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Mục tiêu luyện tập</t>
+          <t>Đã nắm chắc</t>
         </is>
       </c>
     </row>
@@ -32128,7 +32134,7 @@
           <t>Maximum Submatrix 2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>http://codeforces.com/problemset/problem/375/B</t>
         </is>
@@ -32141,21 +32147,27 @@
       <c r="E46" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="21" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+      <c r="F46" s="21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>data structures, dp, implementation, sortings</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành gần đây</t>
         </is>
       </c>
       <c r="I46" s="21" t="inlineStr">
         <is>
-          <t>Chưa nộp</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Mục tiêu luyện tập</t>
+          <t>Đã nắm chắc</t>
         </is>
       </c>
     </row>

--- a/ICPC_OLP_Training_Deruck.xlsx
+++ b/ICPC_OLP_Training_Deruck.xlsx
@@ -11194,7 +11194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -14006,17 +14006,17 @@
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1120/D</t>
+          <t>https://codeforces.com/problemset/problem/1051/F</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu (Ôn lại: 788 ngày)</t>
+          <t>graphs, shortest paths, trees (Ôn lại: 1164 ngày)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="D115" s="18" t="inlineStr"/>
@@ -14026,12 +14026,12 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1051/F</t>
+          <t>https://codeforces.com/problemset/problem/342/E</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>graphs, shortest paths, trees (Ôn lại: 1164 ngày)</t>
+          <t>data structures, divide and conquer, trees (Ôn lại: 1043 ngày)</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
@@ -14046,12 +14046,12 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/342/E</t>
+          <t>https://codeforces.com/problemset/problem/916/E</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, trees (Ôn lại: 1043 ngày)</t>
+          <t>data structures, trees (Ôn lại: 969 ngày)</t>
         </is>
       </c>
       <c r="C117" s="17" t="inlineStr">
@@ -14066,12 +14066,12 @@
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/916/E</t>
+          <t>https://codeforces.com/problemset/problem/915/F</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>data structures, trees (Ôn lại: 969 ngày)</t>
+          <t>data structures, dsu, graphs (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
@@ -14086,12 +14086,12 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/915/F</t>
+          <t>https://codeforces.com/problemset/problem/1709/E</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>data structures, dsu, graphs (Ôn lại: 800 ngày)</t>
+          <t>bitmasks, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C119" s="17" t="inlineStr">
@@ -14106,12 +14106,12 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1709/E</t>
+          <t>https://codeforces.com/problemset/problem/2001/E1</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 786 ngày)</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
@@ -14126,17 +14126,17 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2001/E1</t>
+          <t>https://codeforces.com/problemset/problem/1062/E</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 786 ngày)</t>
+          <t>binary search, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D121" s="18" t="inlineStr"/>
@@ -14146,12 +14146,12 @@
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1062/E</t>
+          <t>https://codeforces.com/problemset/problem/600/E</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
@@ -14166,12 +14166,12 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/600/E</t>
+          <t>https://codeforces.com/problemset/problem/1916/E</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, greedy (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C123" s="17" t="inlineStr">
@@ -14186,12 +14186,12 @@
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1916/E</t>
+          <t>https://codeforces.com/problemset/problem/1824/B2</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, greedy (Ôn lại: 800 ngày)</t>
+          <t>combinatorics, dfs and similar, math (Ôn lại: 794 ngày)</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
@@ -14206,12 +14206,12 @@
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1824/B2</t>
+          <t>https://codeforces.com/problemset/problem/1748/E</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dfs and similar, math (Ôn lại: 794 ngày)</t>
+          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
         </is>
       </c>
       <c r="C125" s="17" t="inlineStr">
@@ -14226,12 +14226,12 @@
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1748/E</t>
+          <t>https://codeforces.com/problemset/problem/2041/I</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
+          <t>binary search, data structures, hashing (Ôn lại: 316 ngày)</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
@@ -14246,17 +14246,17 @@
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/I</t>
+          <t>https://codeforces.com/problemset/problem/979/D</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, hashing (Ôn lại: 316 ngày)</t>
+          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
         </is>
       </c>
       <c r="C127" s="17" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="D127" s="18" t="inlineStr"/>
@@ -14266,12 +14266,12 @@
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/979/D</t>
+          <t>https://codeforces.com/problemset/problem/570/D</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
+          <t>binary search, bitmasks, constructive algorithms (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C128" s="17" t="inlineStr">
@@ -14286,12 +14286,12 @@
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/570/D</t>
+          <t>https://codeforces.com/problemset/problem/337/E</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, constructive algorithms (Ôn lại: 800 ngày)</t>
+          <t>brute force, number theory, trees (Ôn lại: 369 ngày)</t>
         </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
@@ -14306,17 +14306,17 @@
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/337/E</t>
+          <t>https://codeforces.com/problemset/problem/1913/D</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>brute force, number theory, trees (Ôn lại: 369 ngày)</t>
+          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
         </is>
       </c>
       <c r="C130" s="17" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="D130" s="18" t="inlineStr"/>
@@ -14326,17 +14326,17 @@
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1913/D</t>
+          <t>https://codeforces.com/problemset/problem/1857/G</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
+          <t>combinatorics, divide and conquer, dsu (Ôn lại: 1160 ngày)</t>
         </is>
       </c>
       <c r="C131" s="17" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D131" s="18" t="inlineStr"/>
@@ -14346,12 +14346,12 @@
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1857/G</t>
+          <t>https://codeforces.com/problemset/problem/1827/B1</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, divide and conquer, dsu (Ôn lại: 1160 ngày)</t>
+          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C132" s="17" t="inlineStr">
@@ -14366,12 +14366,12 @@
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B1</t>
+          <t>https://codeforces.com/problemset/problem/1923/E</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C133" s="17" t="inlineStr">
@@ -14386,17 +14386,17 @@
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1923/E</t>
+          <t>https://codeforces.com/problemset/problem/1902/E</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
+          <t>data structures, strings, trees (Ôn lại: 1046 ngày)</t>
         </is>
       </c>
       <c r="C134" s="17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D134" s="18" t="inlineStr"/>
@@ -14406,12 +14406,12 @@
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/E</t>
+          <t>https://codeforces.com/problemset/problem/1986/F</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>data structures, strings, trees (Ôn lại: 1046 ngày)</t>
+          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
@@ -14426,12 +14426,12 @@
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1986/F</t>
+          <t>https://codeforces.com/problemset/problem/1994/D</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees (Ôn lại: 844 ngày)</t>
+          <t>constructive algorithms, dsu, graphs (Ôn lại: 819 ngày)</t>
         </is>
       </c>
       <c r="C136" s="17" t="inlineStr">
@@ -14446,12 +14446,12 @@
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1994/D</t>
+          <t>https://codeforces.com/problemset/problem/1895/D</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dsu, graphs (Ôn lại: 819 ngày)</t>
+          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
@@ -14466,12 +14466,12 @@
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1895/D</t>
+          <t>https://codeforces.com/problemset/problem/1899/G</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C138" s="17" t="inlineStr">
@@ -14486,17 +14486,17 @@
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1899/G</t>
+          <t>https://codeforces.com/problemset/problem/706/D</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
+          <t>binary search, bitmasks, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="D139" s="18" t="inlineStr"/>
@@ -14506,12 +14506,12 @@
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/706/D</t>
+          <t>https://codeforces.com/problemset/problem/1824/B1</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, data structures (Ôn lại: 800 ngày)</t>
+          <t>combinatorics, math, probabilities (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C140" s="17" t="inlineStr">
@@ -14526,12 +14526,12 @@
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1824/B1</t>
+          <t>https://codeforces.com/problemset/problem/1856/E1</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, math, probabilities (Ôn lại: 800 ngày)</t>
+          <t>dfs and similar, dp, trees (Ôn lại: 773 ngày)</t>
         </is>
       </c>
       <c r="C141" s="17" t="inlineStr">
@@ -14546,17 +14546,17 @@
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1856/E1</t>
+          <t>https://codeforces.com/problemset/problem/1975/D</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, trees (Ôn lại: 773 ngày)</t>
+          <t>brute force, dfs and similar, dp (Ôn lại: 872 ngày)</t>
         </is>
       </c>
       <c r="C142" s="17" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="D142" s="18" t="inlineStr"/>
@@ -14566,42 +14566,22 @@
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1975/D</t>
+          <t>https://codeforces.com/problemset/problem/1861/C</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, dp (Ôn lại: 872 ngày)</t>
+          <t>data structures, dfs and similar, implementation (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="D143" s="18" t="inlineStr"/>
       <c r="E143" s="18" t="inlineStr"/>
       <c r="F143" s="18" t="inlineStr"/>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="16" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/1861/C</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>data structures, dfs and similar, implementation (Ôn lại: 800 ngày)</t>
-        </is>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="D144" s="18" t="inlineStr"/>
-      <c r="E144" s="18" t="inlineStr"/>
-      <c r="F144" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14614,7 +14594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -16582,12 +16562,12 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1120/D</t>
+          <t>https://codeforces.com/problemset/problem/840/C</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu (Ôn lại: 788 ngày)</t>
+          <t>combinatorics, dp (Ôn lại: 765 ngày)</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
@@ -16602,17 +16582,17 @@
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/840/C</t>
+          <t>https://codeforces.com/problemset/problem/1827/B2</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp (Ôn lại: 765 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="D82" s="18" t="inlineStr"/>
@@ -16622,12 +16602,12 @@
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B2</t>
+          <t>https://codeforces.com/problemset/problem/2001/E1</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 800 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 786 ngày)</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
@@ -16642,17 +16622,17 @@
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2001/E1</t>
+          <t>https://codeforces.com/problemset/problem/623/B</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 786 ngày)</t>
+          <t>dp, greedy, number theory (Ôn lại: 1307 ngày)</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr"/>
@@ -16662,12 +16642,12 @@
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/623/B</t>
+          <t>https://codeforces.com/problemset/problem/1198/D</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>dp, greedy, number theory (Ôn lại: 1307 ngày)</t>
+          <t>dp (Ôn lại: 1041 ngày)</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
@@ -16682,12 +16662,12 @@
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1198/D</t>
+          <t>https://codeforces.com/problemset/problem/1699/D</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>dp (Ôn lại: 1041 ngày)</t>
+          <t>data structures, dp, greedy (Ôn lại: 1041 ngày)</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
@@ -16702,12 +16682,12 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1699/D</t>
+          <t>https://codeforces.com/problemset/problem/808/G</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>data structures, dp, greedy (Ôn lại: 1041 ngày)</t>
+          <t>dp, strings (Ôn lại: 854 ngày)</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
@@ -16722,12 +16702,12 @@
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/808/G</t>
+          <t>https://codeforces.com/problemset/problem/1316/E</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>dp, strings (Ôn lại: 854 ngày)</t>
+          <t>bitmasks, dp, greedy (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
@@ -16742,12 +16722,12 @@
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1316/E</t>
+          <t>https://codeforces.com/problemset/problem/1861/E</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, dp, greedy (Ôn lại: 800 ngày)</t>
+          <t>combinatorics, dp, implementation (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
@@ -16762,12 +16742,12 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1861/E</t>
+          <t>https://codeforces.com/problemset/problem/1748/E</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, implementation (Ôn lại: 800 ngày)</t>
+          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
@@ -16782,12 +16762,12 @@
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1748/E</t>
+          <t>https://codeforces.com/problemset/problem/2041/H</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
+          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
@@ -16802,17 +16782,17 @@
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/H</t>
+          <t>https://codeforces.com/problemset/problem/165/E</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math (Ôn lại: 330 ngày)</t>
+          <t>bitmasks, brute force, dfs and similar (Ôn lại: 1022 ngày)</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr"/>
@@ -16822,12 +16802,12 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/165/E</t>
+          <t>https://codeforces.com/problemset/problem/979/D</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, brute force, dfs and similar (Ôn lại: 1022 ngày)</t>
+          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
@@ -16842,12 +16822,12 @@
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/979/D</t>
+          <t>https://codeforces.com/problemset/problem/1993/D</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
+          <t>binary search, dp, greedy (Ôn lại: 802 ngày)</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
@@ -16862,12 +16842,12 @@
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1993/D</t>
+          <t>https://codeforces.com/problemset/problem/1215/E</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>binary search, dp, greedy (Ôn lại: 802 ngày)</t>
+          <t>bitmasks, dp (Ôn lại: 559 ngày)</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
@@ -16882,12 +16862,12 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1215/E</t>
+          <t>https://codeforces.com/problemset/problem/2045/H</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, dp (Ôn lại: 559 ngày)</t>
+          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
@@ -16902,12 +16882,12 @@
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/H</t>
+          <t>https://codeforces.com/problemset/problem/2030/E</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures (Ôn lại: 358 ngày)</t>
+          <t>combinatorics, data structures, dp (Ôn lại: 323 ngày)</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
@@ -16922,17 +16902,17 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2030/E</t>
+          <t>https://codeforces.com/problemset/problem/1913/D</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, data structures, dp (Ôn lại: 323 ngày)</t>
+          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr"/>
@@ -16942,12 +16922,12 @@
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1913/D</t>
+          <t>https://codeforces.com/problemset/problem/319/C</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
+          <t>dp, geometry (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
@@ -16962,12 +16942,12 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/319/C</t>
+          <t>https://codeforces.com/problemset/problem/1884/D</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>dp, geometry (Ôn lại: 800 ngày)</t>
+          <t>dp, math, number theory (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
@@ -16982,12 +16962,12 @@
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1884/D</t>
+          <t>https://codeforces.com/problemset/problem/354/C</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>dp, math, number theory (Ôn lại: 800 ngày)</t>
+          <t>brute force, dp, number theory (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
@@ -17002,12 +16982,12 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/354/C</t>
+          <t>https://codeforces.com/problemset/problem/1900/E</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>brute force, dp, number theory (Ôn lại: 800 ngày)</t>
+          <t>dfs and similar, dp, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
@@ -17022,12 +17002,12 @@
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1900/E</t>
+          <t>https://codeforces.com/problemset/problem/1998/D</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, dp, graphs (Ôn lại: 796 ngày)</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
@@ -17042,17 +17022,17 @@
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/D</t>
+          <t>https://codeforces.com/problemset/problem/432/D</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>data structures, dp, graphs (Ôn lại: 796 ngày)</t>
+          <t>dp, string suffix structures, strings (Ôn lại: 854 ngày)</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr"/>
@@ -17062,12 +17042,12 @@
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/432/D</t>
+          <t>https://codeforces.com/problemset/problem/346/B</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>dp, string suffix structures, strings (Ôn lại: 854 ngày)</t>
+          <t>dp, strings (Ôn lại: 850 ngày)</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
@@ -17082,12 +17062,12 @@
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/346/B</t>
+          <t>https://codeforces.com/problemset/problem/1827/B1</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>dp, strings (Ôn lại: 850 ngày)</t>
+          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
@@ -17102,12 +17082,12 @@
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B1</t>
+          <t>https://codeforces.com/problemset/problem/1923/E</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
@@ -17122,12 +17102,12 @@
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1923/E</t>
+          <t>https://codeforces.com/problemset/problem/63/E</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
+          <t>bitmasks, dfs and similar, dp (Ôn lại: 765 ngày)</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
@@ -17142,12 +17122,12 @@
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/63/E</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp (Ôn lại: 765 ngày)</t>
+          <t>bitmasks, dfs and similar, dp (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
@@ -17162,17 +17142,17 @@
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/1238/D</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp (Ôn lại: 330 ngày)</t>
+          <t>binary search, combinatorics, dp (Ôn lại: 1434 ngày)</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr"/>
@@ -17182,12 +17162,12 @@
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1238/D</t>
+          <t>https://codeforces.com/problemset/problem/1902/D</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>binary search, combinatorics, dp (Ôn lại: 1434 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 1036 ngày)</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
@@ -17202,12 +17182,12 @@
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/D</t>
+          <t>https://codeforces.com/problemset/problem/1977/C</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 1036 ngày)</t>
+          <t>brute force, data structures, dp (Ôn lại: 872 ngày)</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
@@ -17222,12 +17202,12 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1977/C</t>
+          <t>https://codeforces.com/problemset/problem/2000/F</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>brute force, data structures, dp (Ôn lại: 872 ngày)</t>
+          <t>dp, greedy, implementation (Ôn lại: 793 ngày)</t>
         </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
@@ -17242,12 +17222,12 @@
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2000/F</t>
+          <t>https://codeforces.com/problemset/problem/1906/E</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>dp, greedy, implementation (Ôn lại: 793 ngày)</t>
+          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
@@ -17262,17 +17242,17 @@
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1906/E</t>
+          <t>https://codeforces.com/problemset/problem/1096/D</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp (Ôn lại: 357 ngày)</t>
+          <t>dp (Ôn lại: 1459 ngày)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="D115" s="18" t="inlineStr"/>
@@ -17282,12 +17262,12 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1096/D</t>
+          <t>https://codeforces.com/problemset/problem/1859/D</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>dp (Ôn lại: 1459 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 1155 ngày)</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
@@ -17302,12 +17282,12 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1859/D</t>
+          <t>https://codeforces.com/problemset/problem/1990/D</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 1155 ngày)</t>
+          <t>bitmasks, brute force, dp (Ôn lại: 817 ngày)</t>
         </is>
       </c>
       <c r="C117" s="17" t="inlineStr">
@@ -17322,12 +17302,12 @@
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1990/D</t>
+          <t>https://codeforces.com/problemset/problem/1856/E1</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, brute force, dp (Ôn lại: 817 ngày)</t>
+          <t>dfs and similar, dp, trees (Ôn lại: 773 ngày)</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
@@ -17342,17 +17322,17 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1856/E1</t>
+          <t>https://codeforces.com/problemset/problem/295/B</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, trees (Ôn lại: 773 ngày)</t>
+          <t>dp, graphs, shortest paths (Ôn lại: 1052 ngày)</t>
         </is>
       </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="D119" s="18" t="inlineStr"/>
@@ -17362,12 +17342,12 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/295/B</t>
+          <t>https://codeforces.com/problemset/problem/1975/D</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>dp, graphs, shortest paths (Ôn lại: 1052 ngày)</t>
+          <t>brute force, dfs and similar, dp (Ôn lại: 872 ngày)</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
@@ -17382,12 +17362,12 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1975/D</t>
+          <t>https://codeforces.com/problemset/problem/126/B</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, dp (Ôn lại: 872 ngày)</t>
+          <t>binary search, dp, hashing (Ôn lại: 854 ngày)</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
@@ -17402,12 +17382,12 @@
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/126/B</t>
+          <t>https://codeforces.com/problemset/problem/2181/M</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>binary search, dp, hashing (Ôn lại: 854 ngày)</t>
+          <t>dp, strings (Ôn lại: 70 ngày)</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
@@ -17422,42 +17402,22 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2181/M</t>
+          <t>https://codeforces.com/problemset/problem/1994/C</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>dp, strings (Ôn lại: 70 ngày)</t>
+          <t>binary search, dp, two pointers (Ôn lại: 819 ngày)</t>
         </is>
       </c>
       <c r="C123" s="17" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="D123" s="18" t="inlineStr"/>
       <c r="E123" s="18" t="inlineStr"/>
       <c r="F123" s="18" t="inlineStr"/>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="16" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/1994/C</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>binary search, dp, two pointers (Ôn lại: 819 ngày)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="D124" s="18" t="inlineStr"/>
-      <c r="E124" s="18" t="inlineStr"/>
-      <c r="F124" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17689,17 +17649,17 @@
       <c r="C8" s="17" t="inlineStr"/>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1120/D</t>
+          <t>https://codeforces.com/problemset/problem/375/D</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu (Ôn lại: 788 ngày)</t>
+          <t>data structures, dfs and similar, trees (Ôn lại: 1171 ngày)</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2400</t>
         </is>
       </c>
     </row>
@@ -17717,12 +17677,12 @@
       <c r="C9" s="17" t="inlineStr"/>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/375/D</t>
+          <t>https://codeforces.com/problemset/problem/342/E</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, trees (Ôn lại: 1171 ngày)</t>
+          <t>data structures, divide and conquer, trees (Ôn lại: 1043 ngày)</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -17745,12 +17705,12 @@
       <c r="C10" s="17" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/342/E</t>
+          <t>https://codeforces.com/problemset/problem/916/E</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, trees (Ôn lại: 1043 ngày)</t>
+          <t>data structures, trees (Ôn lại: 969 ngày)</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -17773,12 +17733,12 @@
       <c r="C11" s="17" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/916/E</t>
+          <t>https://codeforces.com/problemset/problem/1827/B2</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>data structures, trees (Ôn lại: 969 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -17801,12 +17761,12 @@
       <c r="C12" s="17" t="inlineStr"/>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B2</t>
+          <t>https://codeforces.com/problemset/problem/1000/F</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 800 ngày)</t>
+          <t>data structures, divide and conquer (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -17829,12 +17789,12 @@
       <c r="C13" s="17" t="inlineStr"/>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1000/F</t>
+          <t>https://codeforces.com/problemset/problem/915/F</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer (Ôn lại: 800 ngày)</t>
+          <t>data structures, dsu, graphs (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -17857,12 +17817,12 @@
       <c r="C14" s="17" t="inlineStr"/>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/915/F</t>
+          <t>https://codeforces.com/problemset/problem/1709/E</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>data structures, dsu, graphs (Ôn lại: 800 ngày)</t>
+          <t>bitmasks, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -17885,17 +17845,17 @@
       <c r="C15" s="17" t="inlineStr"/>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1709/E</t>
+          <t>https://codeforces.com/problemset/problem/786/B</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
+          <t>data structures, graphs, shortest paths (Ôn lại: 1172 ngày)</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
     </row>
@@ -17913,12 +17873,12 @@
       <c r="C16" s="17" t="inlineStr"/>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/786/B</t>
+          <t>https://codeforces.com/problemset/problem/888/G</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>data structures, graphs, shortest paths (Ôn lại: 1172 ngày)</t>
+          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 1054 ngày)</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -17941,12 +17901,12 @@
       <c r="C17" s="17" t="inlineStr"/>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/888/G</t>
+          <t>https://codeforces.com/problemset/problem/825/E</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 1054 ngày)</t>
+          <t>data structures, dfs and similar, graphs (Ôn lại: 1041 ngày)</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -17969,12 +17929,12 @@
       <c r="C18" s="17" t="inlineStr"/>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/825/E</t>
+          <t>https://codeforces.com/problemset/problem/1699/D</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, graphs (Ôn lại: 1041 ngày)</t>
+          <t>data structures, dp, greedy (Ôn lại: 1041 ngày)</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -17997,12 +17957,12 @@
       <c r="C19" s="17" t="inlineStr"/>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1699/D</t>
+          <t>https://codeforces.com/problemset/problem/1062/E</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>data structures, dp, greedy (Ôn lại: 1041 ngày)</t>
+          <t>binary search, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -18025,12 +17985,12 @@
       <c r="C20" s="17" t="inlineStr"/>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1062/E</t>
+          <t>https://codeforces.com/problemset/problem/600/E</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dfs and similar (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -18053,12 +18013,12 @@
       <c r="C21" s="17" t="inlineStr"/>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/600/E</t>
+          <t>https://codeforces.com/problemset/problem/438/D</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, math (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -18085,12 +18045,12 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/438/D</t>
+          <t>https://codeforces.com/problemset/problem/558/E</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>data structures, math (Ôn lại: 800 ngày)</t>
+          <t>data structures, sortings, strings (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -18113,12 +18073,12 @@
       <c r="C23" s="17" t="inlineStr"/>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/558/E</t>
+          <t>https://codeforces.com/problemset/problem/1916/E</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>data structures, sortings, strings (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, greedy (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -18141,12 +18101,12 @@
       <c r="C24" s="17" t="inlineStr"/>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1916/E</t>
+          <t>https://codeforces.com/problemset/problem/1748/E</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, greedy (Ôn lại: 800 ngày)</t>
+          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -18173,12 +18133,12 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1748/E</t>
+          <t>https://codeforces.com/problemset/problem/160/D</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer (Ôn lại: 786 ngày)</t>
+          <t>dfs and similar, dsu, graphs (Ôn lại: 529 ngày)</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -18205,12 +18165,12 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/160/D</t>
+          <t>https://codeforces.com/problemset/problem/2041/I</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dsu, graphs (Ôn lại: 529 ngày)</t>
+          <t>binary search, data structures, hashing (Ôn lại: 316 ngày)</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -18237,17 +18197,17 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/I</t>
+          <t>https://codeforces.com/problemset/problem/86/D</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, hashing (Ôn lại: 316 ngày)</t>
+          <t>data structures, implementation, math (Ôn lại: 1171 ngày)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
     </row>
@@ -18265,12 +18225,12 @@
       <c r="C28" s="17" t="inlineStr"/>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/86/D</t>
+          <t>https://codeforces.com/problemset/problem/617/E</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>data structures, implementation, math (Ôn lại: 1171 ngày)</t>
+          <t>data structures (Ôn lại: 1171 ngày)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -18293,12 +18253,12 @@
       <c r="C29" s="17" t="inlineStr"/>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/617/E</t>
+          <t>https://codeforces.com/problemset/problem/979/D</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>data structures (Ôn lại: 1171 ngày)</t>
+          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -18325,12 +18285,12 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/979/D</t>
+          <t>https://codeforces.com/problemset/problem/1998/E1</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, brute force (Ôn lại: 863 ngày)</t>
+          <t>binary search, brute force, data structures (Ôn lại: 796 ngày)</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -18357,12 +18317,12 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/E1</t>
+          <t>https://codeforces.com/problemset/problem/2030/E</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>binary search, brute force, data structures (Ôn lại: 796 ngày)</t>
+          <t>combinatorics, data structures, dp (Ôn lại: 323 ngày)</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -18385,17 +18345,17 @@
       <c r="C32" s="17" t="inlineStr"/>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2030/E</t>
+          <t>https://codeforces.com/problemset/problem/920/E</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, data structures, dp (Ôn lại: 323 ngày)</t>
+          <t>data structures, dfs and similar, dsu (Ôn lại: 1326 ngày)</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
     </row>
@@ -18417,12 +18377,12 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/920/E</t>
+          <t>https://codeforces.com/problemset/problem/1913/D</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu (Ôn lại: 1326 ngày)</t>
+          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -18445,12 +18405,12 @@
       <c r="C34" s="17" t="inlineStr"/>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1913/D</t>
+          <t>https://codeforces.com/problemset/problem/1900/E</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, dp (Ôn lại: 1027 ngày)</t>
+          <t>dfs and similar, dp, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -18477,12 +18437,12 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1900/E</t>
+          <t>https://codeforces.com/problemset/problem/1998/D</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu (Ôn lại: 800 ngày)</t>
+          <t>data structures, dp, graphs (Ôn lại: 796 ngày)</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -18509,12 +18469,12 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/D</t>
+          <t>https://codeforces.com/problemset/problem/2045/I</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>data structures, dp, graphs (Ôn lại: 796 ngày)</t>
+          <t>data structures (Ôn lại: 358 ngày)</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -18541,12 +18501,12 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/I</t>
+          <t>https://codeforces.com/problemset/problem/1906/F</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>data structures (Ôn lại: 358 ngày)</t>
+          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
@@ -18569,17 +18529,17 @@
       <c r="C38" s="17" t="inlineStr"/>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1906/F</t>
+          <t>https://codeforces.com/problemset/problem/1857/G</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>data structures, sortings (Ôn lại: 357 ngày)</t>
+          <t>combinatorics, divide and conquer, dsu (Ôn lại: 1160 ngày)</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
     </row>
@@ -18601,12 +18561,12 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1857/G</t>
+          <t>https://codeforces.com/problemset/problem/1976/D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, divide and conquer, dsu (Ôn lại: 1160 ngày)</t>
+          <t>binary search, combinatorics, data structures (Ôn lại: 868 ngày)</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -18633,12 +18593,12 @@
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1976/D</t>
+          <t>https://codeforces.com/problemset/problem/1827/B1</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>binary search, combinatorics, data structures (Ôn lại: 868 ngày)</t>
+          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -18661,12 +18621,12 @@
       <c r="C41" s="17" t="inlineStr"/>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B1</t>
+          <t>https://codeforces.com/problemset/problem/842/D</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>binary search, dp, dsu (Ôn lại: 800 ngày)</t>
+          <t>binary search, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -18693,12 +18653,12 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/842/D</t>
+          <t>https://codeforces.com/problemset/problem/1923/E</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -18725,12 +18685,12 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1923/E</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dp (Ôn lại: 800 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -18757,12 +18717,12 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2181/D</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 330 ngày)</t>
+          <t>binary search, data structures, sortings (Ôn lại: 70 ngày)</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -18785,17 +18745,17 @@
       <c r="C45" s="17" t="inlineStr"/>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2181/D</t>
+          <t>https://codeforces.com/problemset/problem/1902/E</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, sortings (Ôn lại: 70 ngày)</t>
+          <t>data structures, strings, trees (Ôn lại: 1046 ngày)</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -18813,12 +18773,12 @@
       <c r="C46" s="17" t="inlineStr"/>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/E</t>
+          <t>https://codeforces.com/problemset/problem/1902/D</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>data structures, strings, trees (Ôn lại: 1046 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 1036 ngày)</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -18841,12 +18801,12 @@
       <c r="C47" s="17" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/D</t>
+          <t>https://codeforces.com/problemset/problem/1977/C</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 1036 ngày)</t>
+          <t>brute force, data structures, dp (Ôn lại: 872 ngày)</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -18869,12 +18829,12 @@
       <c r="C48" s="17" t="inlineStr"/>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1977/C</t>
+          <t>https://codeforces.com/problemset/problem/1994/D</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>brute force, data structures, dp (Ôn lại: 872 ngày)</t>
+          <t>constructive algorithms, dsu, graphs (Ôn lại: 819 ngày)</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -18901,12 +18861,12 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1994/D</t>
+          <t>https://codeforces.com/problemset/problem/1895/D</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, dsu, graphs (Ôn lại: 819 ngày)</t>
+          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -18929,12 +18889,12 @@
       <c r="C50" s="17" t="inlineStr"/>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1895/D</t>
+          <t>https://codeforces.com/problemset/problem/1899/G</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -18957,12 +18917,12 @@
       <c r="C51" s="17" t="inlineStr"/>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1899/G</t>
+          <t>https://codeforces.com/problemset/problem/2001/D</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu (Ôn lại: 800 ngày)</t>
+          <t>brute force, constructive algorithms, data structures (Ôn lại: 785 ngày)</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr">
@@ -18985,17 +18945,17 @@
       <c r="C52" s="17" t="inlineStr"/>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2001/D</t>
+          <t>https://codeforces.com/problemset/problem/221/D</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>brute force, constructive algorithms, data structures (Ôn lại: 785 ngày)</t>
+          <t>data structures (Ôn lại: 1171 ngày)</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1800</t>
         </is>
       </c>
     </row>
@@ -19017,12 +18977,12 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/221/D</t>
+          <t>https://codeforces.com/problemset/problem/1859/D</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>data structures (Ôn lại: 1171 ngày)</t>
+          <t>binary search, data structures, dp (Ôn lại: 1155 ngày)</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -19045,12 +19005,12 @@
       <c r="C54" s="17" t="inlineStr"/>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1859/D</t>
+          <t>https://codeforces.com/problemset/problem/706/D</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp (Ôn lại: 1155 ngày)</t>
+          <t>binary search, bitmasks, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -19073,17 +19033,17 @@
       <c r="C55" s="17" t="inlineStr"/>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/706/D</t>
+          <t>https://codeforces.com/problemset/problem/1894/D</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, data structures (Ôn lại: 800 ngày)</t>
+          <t>constructive algorithms, data structures, sortings (Ôn lại: 1073 ngày)</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1700</t>
         </is>
       </c>
     </row>
@@ -19101,12 +19061,12 @@
       <c r="C56" s="17" t="inlineStr"/>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1894/D</t>
+          <t>https://codeforces.com/problemset/problem/1995/B2</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>constructive algorithms, data structures, sortings (Ôn lại: 1073 ngày)</t>
+          <t>binary search, data structures, greedy (Ôn lại: 814 ngày)</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
@@ -19133,12 +19093,12 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1995/B2</t>
+          <t>https://codeforces.com/problemset/problem/1833/F</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy (Ôn lại: 814 ngày)</t>
+          <t>combinatorics, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -19161,12 +19121,12 @@
       <c r="C58" s="17" t="inlineStr"/>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1833/F</t>
+          <t>https://codeforces.com/problemset/problem/1896/D</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>combinatorics, constructive algorithms, data structures (Ôn lại: 800 ngày)</t>
+          <t>binary search, data structures, divide and conquer (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
@@ -19189,17 +19149,17 @@
       <c r="C59" s="17" t="inlineStr"/>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1896/D</t>
+          <t>https://codeforces.com/problemset/problem/1833/E</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer (Ôn lại: 800 ngày)</t>
+          <t>dfs and similar, dsu, graphs (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
     </row>
@@ -19217,12 +19177,12 @@
       <c r="C60" s="17" t="inlineStr"/>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1833/E</t>
+          <t>https://codeforces.com/problemset/problem/1861/C</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>dfs and similar, dsu, graphs (Ôn lại: 800 ngày)</t>
+          <t>data structures, dfs and similar, implementation (Ôn lại: 800 ngày)</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -19241,12 +19201,12 @@
       <c r="C61" s="17" t="inlineStr"/>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1861/C</t>
+          <t>https://codeforces.com/problemset/problem/2004/D</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, implementation (Ôn lại: 800 ngày)</t>
+          <t>binary search, brute force, data structures (Ôn lại: 791 ngày)</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr">
@@ -19267,21 +19227,9 @@
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr"/>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/2004/D</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>binary search, brute force, data structures (Ôn lại: 791 ngày)</t>
-        </is>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+      <c r="D62" s="18" t="inlineStr"/>
+      <c r="E62" s="18" t="inlineStr"/>
+      <c r="F62" s="18" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
@@ -22694,7 +22642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23515,17 +23463,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>1120D</t>
+          <t>840C</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Power Tree</t>
+          <t>On the Bench</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1120/D</t>
+          <t>https://codeforces.com/problemset/problem/840/C</t>
         </is>
       </c>
       <c r="E16" s="20" t="n">
@@ -23533,22 +23481,22 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu, graphs, greedy</t>
+          <t>combinatorics, dp</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>788 ngày</t>
+          <t>765 ngày</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -23568,40 +23516,40 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>840C</t>
+          <t>375D</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>On the Bench</t>
+          <t>Tree and Queries</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/840/C</t>
+          <t>https://codeforces.com/problemset/problem/375/D</t>
         </is>
       </c>
       <c r="E17" s="20" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, dp</t>
+          <t>data structures, dfs and similar, trees</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>765 ngày</t>
+          <t>1171 ngày</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -23621,17 +23569,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>375D</t>
+          <t>1051F</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tree and Queries</t>
+          <t>The Shortest Statement</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/375/D</t>
+          <t>https://codeforces.com/problemset/problem/1051/F</t>
         </is>
       </c>
       <c r="E18" s="20" t="n">
@@ -23639,22 +23587,22 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, trees</t>
+          <t>graphs, shortest paths, trees</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>1171 ngày</t>
+          <t>1164 ngày</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -23674,17 +23622,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>1051F</t>
+          <t>342E</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>The Shortest Statement</t>
+          <t>Xenia and Tree</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1051/F</t>
+          <t>https://codeforces.com/problemset/problem/342/E</t>
         </is>
       </c>
       <c r="E19" s="20" t="n">
@@ -23692,22 +23640,22 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>graphs, shortest paths, trees</t>
+          <t>data structures, divide and conquer, trees</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>1164 ngày</t>
+          <t>1043 ngày</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -23727,17 +23675,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>342E</t>
+          <t>916E</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Xenia and Tree</t>
+          <t>Jamie and Tree</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/342/E</t>
+          <t>https://codeforces.com/problemset/problem/916/E</t>
         </is>
       </c>
       <c r="E20" s="20" t="n">
@@ -23750,17 +23698,17 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, trees</t>
+          <t>data structures, trees</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>1043 ngày</t>
+          <t>969 ngày</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -23780,17 +23728,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>916E</t>
+          <t>1832D2</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Jamie and Tree</t>
+          <t>Red-Blue Operations (Hard Version)</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/916/E</t>
+          <t>https://codeforces.com/problemset/problem/1832/D2</t>
         </is>
       </c>
       <c r="E21" s="20" t="n">
@@ -23798,22 +23746,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>data structures, trees</t>
+          <t>binary search, constructive algorithms, greedy, implementation, math</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>969 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -23833,17 +23781,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>1832D2</t>
+          <t>1827B2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Red-Blue Operations (Hard Version)</t>
+          <t>Range Sorting (Hard Version)</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1832/D2</t>
+          <t>https://codeforces.com/problemset/problem/1827/B2</t>
         </is>
       </c>
       <c r="E22" s="20" t="n">
@@ -23851,12 +23799,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>binary search, constructive algorithms, greedy, implementation, math</t>
+          <t>binary search, data structures, dp, greedy</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -23886,17 +23834,17 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>1827B2</t>
+          <t>449D</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Range Sorting (Hard Version)</t>
+          <t>Jzzhu and Numbers</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B2</t>
+          <t>https://codeforces.com/problemset/problem/449/D</t>
         </is>
       </c>
       <c r="E23" s="20" t="n">
@@ -23909,7 +23857,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp, greedy</t>
+          <t>bitmasks, combinatorics, dp</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -23939,17 +23887,17 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>449D</t>
+          <t>1000F</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Jzzhu and Numbers</t>
+          <t>One Occurrence</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/449/D</t>
+          <t>https://codeforces.com/problemset/problem/1000/F</t>
         </is>
       </c>
       <c r="E24" s="20" t="n">
@@ -23957,12 +23905,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, combinatorics, dp</t>
+          <t>data structures, divide and conquer</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -23992,17 +23940,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>1000F</t>
+          <t>915F</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>One Occurrence</t>
+          <t>Imbalance Value of a Tree</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1000/F</t>
+          <t>https://codeforces.com/problemset/problem/915/F</t>
         </is>
       </c>
       <c r="E25" s="20" t="n">
@@ -24010,12 +23958,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer</t>
+          <t>data structures, dsu, graphs, trees</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -24045,17 +23993,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>915F</t>
+          <t>1709E</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Imbalance Value of a Tree</t>
+          <t>XOR Tree</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/915/F</t>
+          <t>https://codeforces.com/problemset/problem/1709/E</t>
         </is>
       </c>
       <c r="E26" s="20" t="n">
@@ -24063,12 +24011,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>data structures, dsu, graphs, trees</t>
+          <t>bitmasks, data structures, dfs and similar, dsu, greedy</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -24098,17 +24046,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>1709E</t>
+          <t>2001E1</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>XOR Tree</t>
+          <t>Deterministic Heap (Easy Version)</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1709/E</t>
+          <t>https://codeforces.com/problemset/problem/2001/E1</t>
         </is>
       </c>
       <c r="E27" s="20" t="n">
@@ -24116,22 +24064,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, data structures, dfs and similar, dsu, greedy</t>
+          <t>combinatorics, dp, math, trees</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>786 ngày</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -24151,21 +24099,21 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2001E1</t>
+          <t>623B</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Deterministic Heap (Easy Version)</t>
+          <t>Array GCD</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2001/E1</t>
+          <t>https://codeforces.com/problemset/problem/623/B</t>
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -24174,22 +24122,22 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math, trees</t>
+          <t>dp, greedy, number theory</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>786 ngày</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
-        <is>
-          <t>P2 - Master/TST (2400+)</t>
+          <t>1307 ngày</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Cực kỳ quan trọng (2000-2300)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -24204,17 +24152,17 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>623B</t>
+          <t>786B</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Array GCD</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/623/B</t>
+          <t>https://codeforces.com/problemset/problem/786/B</t>
         </is>
       </c>
       <c r="E29" s="20" t="n">
@@ -24222,22 +24170,22 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>dp, greedy, number theory</t>
+          <t>data structures, graphs, shortest paths</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>1307 ngày</t>
+          <t>1172 ngày</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -24257,17 +24205,17 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>786B</t>
+          <t>888G</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>Xor-MST</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/786/B</t>
+          <t>https://codeforces.com/problemset/problem/888/G</t>
         </is>
       </c>
       <c r="E30" s="20" t="n">
@@ -24275,22 +24223,22 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>data structures, graphs, shortest paths</t>
+          <t>bitmasks, constructive algorithms, data structures</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>1172 ngày</t>
+          <t>1054 ngày</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -24310,17 +24258,17 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>888G</t>
+          <t>825E</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Xor-MST</t>
+          <t>Minimal Labels</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/888/G</t>
+          <t>https://codeforces.com/problemset/problem/825/E</t>
         </is>
       </c>
       <c r="E31" s="20" t="n">
@@ -24333,17 +24281,17 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, data structures</t>
+          <t>data structures, dfs and similar, graphs, greedy</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-12-09</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>1054 ngày</t>
+          <t>1041 ngày</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -24363,17 +24311,17 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>825E</t>
+          <t>1198D</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Minimal Labels</t>
+          <t>Rectangle Painting 1</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/825/E</t>
+          <t>https://codeforces.com/problemset/problem/1198/D</t>
         </is>
       </c>
       <c r="E32" s="20" t="n">
@@ -24381,12 +24329,12 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, graphs, greedy</t>
+          <t>dp</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -24416,17 +24364,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>1198D</t>
+          <t>1699D</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Rectangle Painting 1</t>
+          <t>Almost Triple Deletions</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1198/D</t>
+          <t>https://codeforces.com/problemset/problem/1699/D</t>
         </is>
       </c>
       <c r="E33" s="20" t="n">
@@ -24439,7 +24387,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>dp</t>
+          <t>data structures, dp, greedy</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -24469,17 +24417,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>1699D</t>
+          <t>451E</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Almost Triple Deletions</t>
+          <t>Devu and Flowers</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1699/D</t>
+          <t>https://codeforces.com/problemset/problem/451/E</t>
         </is>
       </c>
       <c r="E34" s="20" t="n">
@@ -24487,22 +24435,22 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>data structures, dp, greedy</t>
+          <t>bitmasks, combinatorics, number theory</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>1041 ngày</t>
+          <t>1024 ngày</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -24522,17 +24470,17 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>451E</t>
+          <t>808G</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Devu and Flowers</t>
+          <t>Anthem of Berland</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/451/E</t>
+          <t>https://codeforces.com/problemset/problem/808/G</t>
         </is>
       </c>
       <c r="E35" s="20" t="n">
@@ -24540,22 +24488,22 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, combinatorics, number theory</t>
+          <t>dp, strings</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>1024 ngày</t>
+          <t>854 ngày</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -24575,17 +24523,17 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>808G</t>
+          <t>1062E</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Anthem of Berland</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/808/G</t>
+          <t>https://codeforces.com/problemset/problem/1062/E</t>
         </is>
       </c>
       <c r="E36" s="20" t="n">
@@ -24593,22 +24541,22 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>dp, strings</t>
+          <t>binary search, data structures, dfs and similar, greedy, trees</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>854 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -24628,17 +24576,17 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>1062E</t>
+          <t>1316E</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Team Building</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1062/E</t>
+          <t>https://codeforces.com/problemset/problem/1316/E</t>
         </is>
       </c>
       <c r="E37" s="20" t="n">
@@ -24646,12 +24594,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, dfs and similar, greedy, trees</t>
+          <t>bitmasks, dp, greedy, sortings</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -24681,17 +24629,17 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>1316E</t>
+          <t>1861E</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Team Building</t>
+          <t>Non-Intersecting Subpermutations</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1316/E</t>
+          <t>https://codeforces.com/problemset/problem/1861/E</t>
         </is>
       </c>
       <c r="E38" s="20" t="n">
@@ -24704,7 +24652,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dp, greedy, sortings</t>
+          <t>combinatorics, dp, implementation, math</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -24734,17 +24682,17 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>1861E</t>
+          <t>600E</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Non-Intersecting Subpermutations</t>
+          <t>Lomsat gelral</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1861/E</t>
+          <t>https://codeforces.com/problemset/problem/600/E</t>
         </is>
       </c>
       <c r="E39" s="20" t="n">
@@ -24752,12 +24700,12 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, dp, implementation, math</t>
+          <t>data structures, dfs and similar, dsu, trees</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -24787,17 +24735,17 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>600E</t>
+          <t>438D</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Lomsat gelral</t>
+          <t>The Child and Sequence</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/600/E</t>
+          <t>https://codeforces.com/problemset/problem/438/D</t>
         </is>
       </c>
       <c r="E40" s="20" t="n">
@@ -24805,12 +24753,12 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu, trees</t>
+          <t>data structures, math</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -24840,17 +24788,17 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>438D</t>
+          <t>558E</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>The Child and Sequence</t>
+          <t>A Simple Task</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/438/D</t>
+          <t>https://codeforces.com/problemset/problem/558/E</t>
         </is>
       </c>
       <c r="E41" s="20" t="n">
@@ -24858,12 +24806,12 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>data structures, math</t>
+          <t>data structures, sortings, strings</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
@@ -24893,17 +24841,17 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>558E</t>
+          <t>1916E</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>A Simple Task</t>
+          <t>Happy Life in University</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/558/E</t>
+          <t>https://codeforces.com/problemset/problem/1916/E</t>
         </is>
       </c>
       <c r="E42" s="20" t="n">
@@ -24911,12 +24859,12 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>data structures, sortings, strings</t>
+          <t>data structures, dfs and similar, greedy, trees</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
@@ -24946,17 +24894,17 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>1916E</t>
+          <t>1824B2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Happy Life in University</t>
+          <t>LuoTianyi and the Floating Islands (Hard Version)</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1916/E</t>
+          <t>https://codeforces.com/problemset/problem/1824/B2</t>
         </is>
       </c>
       <c r="E43" s="20" t="n">
@@ -24969,17 +24917,17 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, greedy, trees</t>
+          <t>combinatorics, dfs and similar, math, probabilities, trees</t>
         </is>
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>794 ngày</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -24999,17 +24947,17 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>1824B2</t>
+          <t>1748E</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>LuoTianyi and the Floating Islands (Hard Version)</t>
+          <t>Yet Another Array Counting Problem</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1824/B2</t>
+          <t>https://codeforces.com/problemset/problem/1748/E</t>
         </is>
       </c>
       <c r="E44" s="20" t="n">
@@ -25017,22 +24965,22 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, dfs and similar, math, probabilities, trees</t>
+          <t>binary search, data structures, divide and conquer, dp, flows</t>
         </is>
       </c>
       <c r="H44" s="21" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>794 ngày</t>
+          <t>786 ngày</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -25052,17 +25000,17 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>1748E</t>
+          <t>160D</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Yet Another Array Counting Problem</t>
+          <t>Edges in MST</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1748/E</t>
+          <t>https://codeforces.com/problemset/problem/160/D</t>
         </is>
       </c>
       <c r="E45" s="20" t="n">
@@ -25070,22 +25018,22 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer, dp, flows</t>
+          <t>dfs and similar, dsu, graphs, sortings</t>
         </is>
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>786 ngày</t>
+          <t>529 ngày</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -25105,17 +25053,17 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>160D</t>
+          <t>2041H</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Edges in MST</t>
+          <t>Sheet Music</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/160/D</t>
+          <t>https://codeforces.com/problemset/problem/2041/H</t>
         </is>
       </c>
       <c r="E46" s="20" t="n">
@@ -25123,22 +25071,22 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, dsu, graphs, sortings</t>
+          <t>combinatorics, dp, math</t>
         </is>
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>529 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -25158,17 +25106,17 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>2041H</t>
+          <t>2041I</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Sheet Music</t>
+          <t>Auto Complete</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/H</t>
+          <t>https://codeforces.com/problemset/problem/2041/I</t>
         </is>
       </c>
       <c r="E47" s="20" t="n">
@@ -25176,22 +25124,22 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, dp, math</t>
+          <t>binary search, data structures, hashing, implementation, sortings</t>
         </is>
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>330 ngày</t>
+          <t>316 ngày</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -25211,40 +25159,40 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>2041I</t>
+          <t>86D</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Auto Complete</t>
+          <t>Powerful array</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/I</t>
+          <t>https://codeforces.com/problemset/problem/86/D</t>
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, hashing, implementation, sortings</t>
+          <t>data structures, implementation, math, two pointers</t>
         </is>
       </c>
       <c r="H48" s="21" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>316 ngày</t>
+          <t>1171 ngày</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -25264,17 +25212,17 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>86D</t>
+          <t>617E</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Powerful array</t>
+          <t>XOR and Favorite Number</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/86/D</t>
+          <t>https://codeforces.com/problemset/problem/617/E</t>
         </is>
       </c>
       <c r="E49" s="20" t="n">
@@ -25287,7 +25235,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>data structures, implementation, math, two pointers</t>
+          <t>data structures</t>
         </is>
       </c>
       <c r="H49" s="21" t="inlineStr">
@@ -25317,17 +25265,17 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>617E</t>
+          <t>165E</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XOR and Favorite Number</t>
+          <t>Compatible Numbers</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/617/E</t>
+          <t>https://codeforces.com/problemset/problem/165/E</t>
         </is>
       </c>
       <c r="E50" s="20" t="n">
@@ -25335,22 +25283,22 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>data structures</t>
+          <t>bitmasks, brute force, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H50" s="21" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>1171 ngày</t>
+          <t>1022 ngày</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -25370,17 +25318,17 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>165E</t>
+          <t>979D</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Compatible Numbers</t>
+          <t>Kuro and GCD and XOR and SUM</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/165/E</t>
+          <t>https://codeforces.com/problemset/problem/979/D</t>
         </is>
       </c>
       <c r="E51" s="20" t="n">
@@ -25388,22 +25336,22 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, brute force, dfs and similar, dp</t>
+          <t>binary search, bitmasks, brute force, data structures, dp</t>
         </is>
       </c>
       <c r="H51" s="21" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>1022 ngày</t>
+          <t>863 ngày</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -25423,17 +25371,17 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>979D</t>
+          <t>1993D</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Kuro and GCD and XOR and SUM</t>
+          <t>Med-imize</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/979/D</t>
+          <t>https://codeforces.com/problemset/problem/1993/D</t>
         </is>
       </c>
       <c r="E52" s="20" t="n">
@@ -25446,17 +25394,17 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, brute force, data structures, dp</t>
+          <t>binary search, dp, greedy</t>
         </is>
       </c>
       <c r="H52" s="21" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>863 ngày</t>
+          <t>802 ngày</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -25476,17 +25424,17 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>1993D</t>
+          <t>570D</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Med-imize</t>
+          <t>Tree Requests</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1993/D</t>
+          <t>https://codeforces.com/problemset/problem/570/D</t>
         </is>
       </c>
       <c r="E53" s="20" t="n">
@@ -25494,22 +25442,22 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>binary search, dp, greedy</t>
+          <t>binary search, bitmasks, constructive algorithms, dfs and similar, graphs</t>
         </is>
       </c>
       <c r="H53" s="21" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>802 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -25529,17 +25477,17 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>570D</t>
+          <t>1998E1</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Tree Requests</t>
+          <t>Eliminating Balls With Merging (Easy Version)</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/570/D</t>
+          <t>https://codeforces.com/problemset/problem/1998/E1</t>
         </is>
       </c>
       <c r="E54" s="20" t="n">
@@ -25547,22 +25495,22 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, constructive algorithms, dfs and similar, graphs</t>
+          <t>binary search, brute force, data structures, divide and conquer, greedy</t>
         </is>
       </c>
       <c r="H54" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>796 ngày</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -25582,17 +25530,17 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>1998E1</t>
+          <t>1215E</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Eliminating Balls With Merging (Easy Version)</t>
+          <t>Marbles</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/E1</t>
+          <t>https://codeforces.com/problemset/problem/1215/E</t>
         </is>
       </c>
       <c r="E55" s="20" t="n">
@@ -25600,22 +25548,22 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>binary search, brute force, data structures, divide and conquer, greedy</t>
+          <t>bitmasks, dp</t>
         </is>
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>796 ngày</t>
+          <t>559 ngày</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
@@ -25635,17 +25583,17 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>1215E</t>
+          <t>337E</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Marbles</t>
+          <t>Divisor Tree</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1215/E</t>
+          <t>https://codeforces.com/problemset/problem/337/E</t>
         </is>
       </c>
       <c r="E56" s="20" t="n">
@@ -25653,22 +25601,22 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dp</t>
+          <t>brute force, number theory, trees</t>
         </is>
       </c>
       <c r="H56" s="21" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>559 ngày</t>
+          <t>369 ngày</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -25688,17 +25636,17 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>337E</t>
+          <t>2045H</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Divisor Tree</t>
+          <t>Missing Separators</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/337/E</t>
+          <t>https://codeforces.com/problemset/problem/2045/H</t>
         </is>
       </c>
       <c r="E57" s="20" t="n">
@@ -25706,22 +25654,22 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>brute force, number theory, trees</t>
+          <t>dp, sortings, string suffix structures, strings</t>
         </is>
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>369 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
@@ -25741,17 +25689,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>2045H</t>
+          <t>2030E</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Missing Separators</t>
+          <t>MEXimize the Score</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/H</t>
+          <t>https://codeforces.com/problemset/problem/2030/E</t>
         </is>
       </c>
       <c r="E58" s="20" t="n">
@@ -25764,17 +25712,17 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>dp, sortings, string suffix structures, strings</t>
+          <t>combinatorics, data structures, dp, greedy, implementation</t>
         </is>
       </c>
       <c r="H58" s="21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>323 ngày</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -25794,40 +25742,40 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>2030E</t>
+          <t>920E</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>MEXimize the Score</t>
+          <t>Connected Components?</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2030/E</t>
+          <t>https://codeforces.com/problemset/problem/920/E</t>
         </is>
       </c>
       <c r="E59" s="20" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, data structures, dp, greedy, implementation</t>
+          <t>data structures, dfs and similar, dsu, graphs</t>
         </is>
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>323 ngày</t>
+          <t>1326 ngày</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -25847,17 +25795,17 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>920E</t>
+          <t>1913D</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Connected Components?</t>
+          <t>Array Collapse</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/920/E</t>
+          <t>https://codeforces.com/problemset/problem/1913/D</t>
         </is>
       </c>
       <c r="E60" s="20" t="n">
@@ -25865,22 +25813,22 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu, graphs</t>
+          <t>data structures, divide and conquer, dp, trees</t>
         </is>
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>1326 ngày</t>
+          <t>1027 ngày</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -25900,17 +25848,17 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>1913D</t>
+          <t>1832D1</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Array Collapse</t>
+          <t>Red-Blue Operations (Easy Version)</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1913/D</t>
+          <t>https://codeforces.com/problemset/problem/1832/D1</t>
         </is>
       </c>
       <c r="E61" s="20" t="n">
@@ -25918,22 +25866,22 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>data structures, divide and conquer, dp, trees</t>
+          <t>binary search, greedy, implementation, math</t>
         </is>
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>1027 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -25953,17 +25901,17 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>1832D1</t>
+          <t>319C</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Red-Blue Operations (Easy Version)</t>
+          <t>Kalila and Dimna in the Logging Industry</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1832/D1</t>
+          <t>https://codeforces.com/problemset/problem/319/C</t>
         </is>
       </c>
       <c r="E62" s="20" t="n">
@@ -25971,12 +25919,12 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>binary search, greedy, implementation, math</t>
+          <t>dp, geometry</t>
         </is>
       </c>
       <c r="H62" s="21" t="inlineStr">
@@ -26006,17 +25954,17 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>319C</t>
+          <t>1884D</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Kalila and Dimna in the Logging Industry</t>
+          <t>Counting Rhyme</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/319/C</t>
+          <t>https://codeforces.com/problemset/problem/1884/D</t>
         </is>
       </c>
       <c r="E63" s="20" t="n">
@@ -26029,7 +25977,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>dp, geometry</t>
+          <t>dp, math, number theory</t>
         </is>
       </c>
       <c r="H63" s="21" t="inlineStr">
@@ -26059,17 +26007,17 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>1884D</t>
+          <t>354C</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Counting Rhyme</t>
+          <t>Vasya and Beautiful Arrays</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1884/D</t>
+          <t>https://codeforces.com/problemset/problem/354/C</t>
         </is>
       </c>
       <c r="E64" s="20" t="n">
@@ -26082,7 +26030,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>dp, math, number theory</t>
+          <t>brute force, dp, number theory</t>
         </is>
       </c>
       <c r="H64" s="21" t="inlineStr">
@@ -26112,17 +26060,17 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>354C</t>
+          <t>1900E</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Vasya and Beautiful Arrays</t>
+          <t>Transitive Graph</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/354/C</t>
+          <t>https://codeforces.com/problemset/problem/1900/E</t>
         </is>
       </c>
       <c r="E65" s="20" t="n">
@@ -26130,12 +26078,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>brute force, dp, number theory</t>
+          <t>dfs and similar, dp, dsu, graphs, implementation</t>
         </is>
       </c>
       <c r="H65" s="21" t="inlineStr">
@@ -26165,17 +26113,17 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>1900E</t>
+          <t>1998D</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Transitive Graph</t>
+          <t>Determine Winning Islands in Race</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1900/E</t>
+          <t>https://codeforces.com/problemset/problem/1998/D</t>
         </is>
       </c>
       <c r="E66" s="20" t="n">
@@ -26183,22 +26131,22 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, dsu, graphs, implementation</t>
+          <t>data structures, dp, graphs, greedy, shortest paths</t>
         </is>
       </c>
       <c r="H66" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>796 ngày</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -26218,17 +26166,17 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>1998D</t>
+          <t>2004E</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Determine Winning Islands in Race</t>
+          <t>Not a Nim Problem</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/D</t>
+          <t>https://codeforces.com/problemset/problem/2004/E</t>
         </is>
       </c>
       <c r="E67" s="20" t="n">
@@ -26236,22 +26184,22 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>data structures, dp, graphs, greedy, shortest paths</t>
+          <t>brute force, games, math, number theory</t>
         </is>
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>796 ngày</t>
+          <t>791 ngày</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -26271,17 +26219,17 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>2004E</t>
+          <t>2045I</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Not a Nim Problem</t>
+          <t>Microwavable Subsequence</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2004/E</t>
+          <t>https://codeforces.com/problemset/problem/2045/I</t>
         </is>
       </c>
       <c r="E68" s="20" t="n">
@@ -26289,22 +26237,22 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>brute force, games, math, number theory</t>
+          <t>data structures</t>
         </is>
       </c>
       <c r="H68" s="21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>791 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -26324,17 +26272,17 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>2045I</t>
+          <t>1906F</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Microwavable Subsequence</t>
+          <t>Maximize The Value</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/I</t>
+          <t>https://codeforces.com/problemset/problem/1906/F</t>
         </is>
       </c>
       <c r="E69" s="20" t="n">
@@ -26347,17 +26295,17 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>data structures</t>
+          <t>data structures, sortings</t>
         </is>
       </c>
       <c r="H69" s="21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -26377,17 +26325,17 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>1906F</t>
+          <t>2172K</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Maximize The Value</t>
+          <t>Kindergarten Homework</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1906/F</t>
+          <t>https://codeforces.com/problemset/problem/2172/K</t>
         </is>
       </c>
       <c r="E70" s="20" t="n">
@@ -26400,17 +26348,17 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>data structures, sortings</t>
+          <t>implementation, strings</t>
         </is>
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>357 ngày</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>88 ngày</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -26430,40 +26378,40 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>2172K</t>
+          <t>1311D</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Kindergarten Homework</t>
+          <t>Three Integers</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2172/K</t>
+          <t>https://codeforces.com/problemset/problem/1311/D</t>
         </is>
       </c>
       <c r="E71" s="20" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>implementation, strings</t>
+          <t>brute force, math</t>
         </is>
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>88 ngày</t>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>1431 ngày</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -26483,17 +26431,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>1311D</t>
+          <t>1857G</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Three Integers</t>
+          <t>Counting Graphs</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1311/D</t>
+          <t>https://codeforces.com/problemset/problem/1857/G</t>
         </is>
       </c>
       <c r="E72" s="20" t="n">
@@ -26501,22 +26449,22 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>brute force, math</t>
+          <t>combinatorics, divide and conquer, dsu, graphs, greedy</t>
         </is>
       </c>
       <c r="H72" s="21" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>1431 ngày</t>
+          <t>1160 ngày</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -26536,17 +26484,17 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>1857G</t>
+          <t>1976D</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Counting Graphs</t>
+          <t>Invertible Bracket Sequences</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1857/G</t>
+          <t>https://codeforces.com/problemset/problem/1976/D</t>
         </is>
       </c>
       <c r="E73" s="20" t="n">
@@ -26554,22 +26502,22 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, divide and conquer, dsu, graphs, greedy</t>
+          <t>binary search, combinatorics, data structures, divide and conquer, implementation</t>
         </is>
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>1160 ngày</t>
+          <t>868 ngày</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
@@ -26589,17 +26537,17 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>1976D</t>
+          <t>432D</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Invertible Bracket Sequences</t>
+          <t>Prefixes and Suffixes</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1976/D</t>
+          <t>https://codeforces.com/problemset/problem/432/D</t>
         </is>
       </c>
       <c r="E74" s="20" t="n">
@@ -26607,22 +26555,22 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>binary search, combinatorics, data structures, divide and conquer, implementation</t>
+          <t>dp, string suffix structures, strings, two pointers</t>
         </is>
       </c>
       <c r="H74" s="21" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>868 ngày</t>
+          <t>854 ngày</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -26642,17 +26590,17 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>432D</t>
+          <t>346B</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Prefixes and Suffixes</t>
+          <t>Lucky Common Subsequence</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/432/D</t>
+          <t>https://codeforces.com/problemset/problem/346/B</t>
         </is>
       </c>
       <c r="E75" s="20" t="n">
@@ -26665,17 +26613,17 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>dp, string suffix structures, strings, two pointers</t>
+          <t>dp, strings</t>
         </is>
       </c>
       <c r="H75" s="21" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>854 ngày</t>
+          <t>850 ngày</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
@@ -26695,17 +26643,17 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>346B</t>
+          <t>1827B1</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Lucky Common Subsequence</t>
+          <t>Range Sorting (Easy Version)</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/346/B</t>
+          <t>https://codeforces.com/problemset/problem/1827/B1</t>
         </is>
       </c>
       <c r="E76" s="20" t="n">
@@ -26718,17 +26666,17 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>dp, strings</t>
+          <t>binary search, dp, dsu, greedy, trees</t>
         </is>
       </c>
       <c r="H76" s="21" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>850 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -26748,17 +26696,17 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>1827B1</t>
+          <t>842D</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Range Sorting (Easy Version)</t>
+          <t>Vitya and Strange Lesson</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1827/B1</t>
+          <t>https://codeforces.com/problemset/problem/842/D</t>
         </is>
       </c>
       <c r="E77" s="20" t="n">
@@ -26766,12 +26714,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>binary search, dp, dsu, greedy, trees</t>
+          <t>binary search, data structures</t>
         </is>
       </c>
       <c r="H77" s="21" t="inlineStr">
@@ -26801,17 +26749,17 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>842D</t>
+          <t>1872G</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Vitya and Strange Lesson</t>
+          <t>Replace With Product</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/842/D</t>
+          <t>https://codeforces.com/problemset/problem/1872/G</t>
         </is>
       </c>
       <c r="E78" s="20" t="n">
@@ -26819,12 +26767,12 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures</t>
+          <t>brute force, greedy, math</t>
         </is>
       </c>
       <c r="H78" s="21" t="inlineStr">
@@ -26854,17 +26802,17 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>1872G</t>
+          <t>1923E</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Replace With Product</t>
+          <t>Count Paths</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1872/G</t>
+          <t>https://codeforces.com/problemset/problem/1923/E</t>
         </is>
       </c>
       <c r="E79" s="20" t="n">
@@ -26872,12 +26820,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>brute force, greedy, math</t>
+          <t>data structures, dfs and similar, dp, dsu, graphs</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -26907,17 +26855,17 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>1923E</t>
+          <t>63E</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Count Paths</t>
+          <t>Sweets Game</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1923/E</t>
+          <t>https://codeforces.com/problemset/problem/63/E</t>
         </is>
       </c>
       <c r="E80" s="20" t="n">
@@ -26930,17 +26878,17 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dp, dsu, graphs</t>
+          <t>bitmasks, dfs and similar, dp, games, implementation</t>
         </is>
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>765 ngày</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -26960,17 +26908,17 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>63E</t>
+          <t>2045B</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Sweets Game</t>
+          <t>ICPC Square</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/63/E</t>
+          <t>https://codeforces.com/problemset/problem/2045/B</t>
         </is>
       </c>
       <c r="E81" s="20" t="n">
@@ -26978,22 +26926,22 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp, games, implementation</t>
+          <t>math, number theory</t>
         </is>
       </c>
       <c r="H81" s="21" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>765 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -27013,17 +26961,17 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>2045B</t>
+          <t>2172I</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>ICPC Square</t>
+          <t>Birthday</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/B</t>
+          <t>https://codeforces.com/problemset/problem/2172/I</t>
         </is>
       </c>
       <c r="E82" s="20" t="n">
@@ -27031,22 +26979,22 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Geometry &amp; Sweepline</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>math, number theory</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -27066,17 +27014,17 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>2172I</t>
+          <t>2041M</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Selection Sort</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2172/I</t>
+          <t>https://codeforces.com/problemset/problem/2041/M</t>
         </is>
       </c>
       <c r="E83" s="20" t="n">
@@ -27084,22 +27032,22 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Geometry &amp; Sweepline</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>geometry</t>
+          <t>binary search, data structures, greedy, two pointers</t>
         </is>
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>332 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
@@ -27119,17 +27067,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2041M</t>
+          <t>2041C</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Selection Sort</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/C</t>
         </is>
       </c>
       <c r="E84" s="20" t="n">
@@ -27137,12 +27085,12 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, two pointers</t>
+          <t>bitmasks, dfs and similar, dp</t>
         </is>
       </c>
       <c r="H84" s="21" t="inlineStr">
@@ -27172,17 +27120,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2041C</t>
+          <t>2181D</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Doorway</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/C</t>
+          <t>https://codeforces.com/problemset/problem/2181/D</t>
         </is>
       </c>
       <c r="E85" s="20" t="n">
@@ -27190,22 +27138,22 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, dfs and similar, dp</t>
+          <t>binary search, data structures, sortings</t>
         </is>
       </c>
       <c r="H85" s="21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="I85" s="12" t="inlineStr">
-        <is>
-          <t>330 ngày</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>70 ngày</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
@@ -27225,45 +27173,45 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>2181D</t>
+          <t>1238D</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Doorway</t>
+          <t>AB-string</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2181/D</t>
+          <t>https://codeforces.com/problemset/problem/1238/D</t>
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, sortings</t>
+          <t>binary search, combinatorics, dp, strings</t>
         </is>
       </c>
       <c r="H86" s="21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>70 ngày</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>1434 ngày</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>P1 - Cực kỳ quan trọng (2000-2300)</t>
+          <t>P1 - Trọng tâm ICPC/OLP (1800-1900)</t>
         </is>
       </c>
       <c r="K86" s="21" t="inlineStr">
@@ -27278,17 +27226,17 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>1238D</t>
+          <t>1891D</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>AB-string</t>
+          <t>Suspicious logarithms</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1238/D</t>
+          <t>https://codeforces.com/problemset/problem/1891/D</t>
         </is>
       </c>
       <c r="E87" s="20" t="n">
@@ -27296,22 +27244,22 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>binary search, combinatorics, dp, strings</t>
+          <t>binary search, brute force, math</t>
         </is>
       </c>
       <c r="H87" s="21" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>1434 ngày</t>
+          <t>1080 ngày</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
@@ -27331,17 +27279,17 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>1891D</t>
+          <t>1902E</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Suspicious logarithms</t>
+          <t>Collapsing Strings</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1891/D</t>
+          <t>https://codeforces.com/problemset/problem/1902/E</t>
         </is>
       </c>
       <c r="E88" s="20" t="n">
@@ -27349,22 +27297,22 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>binary search, brute force, math</t>
+          <t>data structures, strings, trees</t>
         </is>
       </c>
       <c r="H88" s="21" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>1080 ngày</t>
+          <t>1046 ngày</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
@@ -27384,17 +27332,17 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>1902E</t>
+          <t>1902D</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Collapsing Strings</t>
+          <t>Robot Queries</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/E</t>
+          <t>https://codeforces.com/problemset/problem/1902/D</t>
         </is>
       </c>
       <c r="E89" s="20" t="n">
@@ -27402,22 +27350,22 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>data structures, strings, trees</t>
+          <t>binary search, data structures, dp, implementation</t>
         </is>
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>1046 ngày</t>
+          <t>1036 ngày</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -27437,17 +27385,17 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>1902D</t>
+          <t>1977C</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Robot Queries</t>
+          <t>Nikita and LCM</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1902/D</t>
+          <t>https://codeforces.com/problemset/problem/1977/C</t>
         </is>
       </c>
       <c r="E90" s="20" t="n">
@@ -27460,17 +27408,17 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp, implementation</t>
+          <t>brute force, data structures, dp, greedy, math</t>
         </is>
       </c>
       <c r="H90" s="21" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>1036 ngày</t>
+          <t>872 ngày</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
@@ -27490,17 +27438,17 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>1977C</t>
+          <t>1986F</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Nikita and LCM</t>
+          <t>Non-academic Problem</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1977/C</t>
+          <t>https://codeforces.com/problemset/problem/1986/F</t>
         </is>
       </c>
       <c r="E91" s="20" t="n">
@@ -27508,22 +27456,22 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>brute force, data structures, dp, greedy, math</t>
+          <t>dfs and similar, graphs, trees</t>
         </is>
       </c>
       <c r="H91" s="21" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>872 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
@@ -27543,17 +27491,17 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>1986F</t>
+          <t>1994D</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Non-academic Problem</t>
+          <t>Funny Game</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1986/F</t>
+          <t>https://codeforces.com/problemset/problem/1994/D</t>
         </is>
       </c>
       <c r="E92" s="20" t="n">
@@ -27561,22 +27509,22 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, trees</t>
+          <t>constructive algorithms, dsu, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H92" s="21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>844 ngày</t>
+          <t>819 ngày</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -27596,17 +27544,17 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>1994D</t>
+          <t>1991E</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Funny Game</t>
+          <t>Coloring Game</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1994/D</t>
+          <t>https://codeforces.com/problemset/problem/1991/E</t>
         </is>
       </c>
       <c r="E93" s="20" t="n">
@@ -27614,22 +27562,22 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dsu, graphs, greedy, math</t>
+          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
         </is>
       </c>
       <c r="H93" s="21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>819 ngày</t>
+          <t>809 ngày</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
@@ -27649,17 +27597,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1991E</t>
+          <t>1991D</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Coloring Game</t>
+          <t>Prime XOR Coloring</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/E</t>
+          <t>https://codeforces.com/problemset/problem/1991/D</t>
         </is>
       </c>
       <c r="E94" s="20" t="n">
@@ -27667,12 +27615,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dfs and similar, games, graphs, greedy</t>
+          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -27702,17 +27650,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1991D</t>
+          <t>1895D</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Prime XOR Coloring</t>
+          <t>XOR Construction</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1991/D</t>
+          <t>https://codeforces.com/problemset/problem/1895/D</t>
         </is>
       </c>
       <c r="E95" s="20" t="n">
@@ -27725,17 +27673,17 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, graphs, greedy, math</t>
+          <t>bitmasks, constructive algorithms, data structures, math, string suffix structures</t>
         </is>
       </c>
       <c r="H95" s="21" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>809 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
@@ -27755,17 +27703,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>1895D</t>
+          <t>1899G</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>XOR Construction</t>
+          <t>Unusual Entertainment</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1895/D</t>
+          <t>https://codeforces.com/problemset/problem/1899/G</t>
         </is>
       </c>
       <c r="E96" s="20" t="n">
@@ -27773,12 +27721,12 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, constructive algorithms, data structures, math, string suffix structures</t>
+          <t>data structures, dfs and similar, dsu, shortest paths, sortings</t>
         </is>
       </c>
       <c r="H96" s="21" t="inlineStr">
@@ -27808,17 +27756,17 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>1899G</t>
+          <t>1998C</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Unusual Entertainment</t>
+          <t>Perform Operations to Maximize Score</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1899/G</t>
+          <t>https://codeforces.com/problemset/problem/1998/C</t>
         </is>
       </c>
       <c r="E97" s="20" t="n">
@@ -27826,22 +27774,22 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, dsu, shortest paths, sortings</t>
+          <t>binary search, brute force, constructive algorithms, greedy, implementation</t>
         </is>
       </c>
       <c r="H97" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>796 ngày</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
@@ -27861,17 +27809,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>1998C</t>
+          <t>2000F</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Perform Operations to Maximize Score</t>
+          <t>Color Rows and Columns</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1998/C</t>
+          <t>https://codeforces.com/problemset/problem/2000/F</t>
         </is>
       </c>
       <c r="E98" s="20" t="n">
@@ -27879,22 +27827,22 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>binary search, brute force, constructive algorithms, greedy, implementation</t>
+          <t>dp, greedy, implementation, math</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>796 ngày</t>
+          <t>793 ngày</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -27914,17 +27862,17 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>2000F</t>
+          <t>2001D</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Color Rows and Columns</t>
+          <t>Longest Max Min Subsequence</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2000/F</t>
+          <t>https://codeforces.com/problemset/problem/2001/D</t>
         </is>
       </c>
       <c r="E99" s="20" t="n">
@@ -27932,22 +27880,22 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>dp, greedy, implementation, math</t>
+          <t>brute force, constructive algorithms, data structures, greedy, implementation</t>
         </is>
       </c>
       <c r="H99" s="21" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>793 ngày</t>
+          <t>785 ngày</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
@@ -27967,17 +27915,17 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>2001D</t>
+          <t>1906E</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Longest Max Min Subsequence</t>
+          <t>Merge Not Sort</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2001/D</t>
+          <t>https://codeforces.com/problemset/problem/1906/E</t>
         </is>
       </c>
       <c r="E100" s="20" t="n">
@@ -27985,22 +27933,22 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>brute force, constructive algorithms, data structures, greedy, implementation</t>
+          <t>constructive algorithms, dp</t>
         </is>
       </c>
       <c r="H100" s="21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>785 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
@@ -28020,17 +27968,17 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>1906E</t>
+          <t>2231D</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Merge Not Sort</t>
+          <t>Maximum Prefix Sums</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1906/E</t>
+          <t>https://codeforces.com/problemset/problem/2231/D</t>
         </is>
       </c>
       <c r="E101" s="20" t="n">
@@ -28038,22 +27986,22 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, dp</t>
+          <t>constructive algorithms, greedy, implementation, two pointers</t>
         </is>
       </c>
       <c r="H101" s="21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>357 ngày</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>141 ngày</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -28073,40 +28021,40 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>2231D</t>
+          <t>1096D</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Maximum Prefix Sums</t>
+          <t>Easy Problem</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2231/D</t>
+          <t>https://codeforces.com/problemset/problem/1096/D</t>
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, greedy, implementation, two pointers</t>
+          <t>dp</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>141 ngày</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>1459 ngày</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -28126,17 +28074,17 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>1096D</t>
+          <t>221D</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Easy Problem</t>
+          <t>Little Elephant and Array</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1096/D</t>
+          <t>https://codeforces.com/problemset/problem/221/D</t>
         </is>
       </c>
       <c r="E103" s="20" t="n">
@@ -28144,22 +28092,22 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>General CP</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>dp</t>
+          <t>data structures</t>
         </is>
       </c>
       <c r="H103" s="21" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>1459 ngày</t>
+          <t>1171 ngày</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
@@ -28179,17 +28127,17 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>221D</t>
+          <t>1859D</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Little Elephant and Array</t>
+          <t>Andrey and Escape from Capygrad</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/221/D</t>
+          <t>https://codeforces.com/problemset/problem/1859/D</t>
         </is>
       </c>
       <c r="E104" s="20" t="n">
@@ -28197,22 +28145,22 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>data structures</t>
+          <t>binary search, data structures, dp, dsu, greedy</t>
         </is>
       </c>
       <c r="H104" s="21" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>1171 ngày</t>
+          <t>1155 ngày</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -28232,17 +28180,17 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>1859D</t>
+          <t>1966D</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Andrey and Escape from Capygrad</t>
+          <t>Missing Subsequence Sum</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1859/D</t>
+          <t>https://codeforces.com/problemset/problem/1966/D</t>
         </is>
       </c>
       <c r="E105" s="20" t="n">
@@ -28250,22 +28198,22 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, dp, dsu, greedy</t>
+          <t>constructive algorithms, greedy, math, number theory</t>
         </is>
       </c>
       <c r="H105" s="21" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>1155 ngày</t>
+          <t>901 ngày</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
@@ -28285,17 +28233,17 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>1966D</t>
+          <t>471D</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Missing Subsequence Sum</t>
+          <t>MUH and Cube Walls</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1966/D</t>
+          <t>https://codeforces.com/problemset/problem/471/D</t>
         </is>
       </c>
       <c r="E106" s="20" t="n">
@@ -28303,22 +28251,22 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Strings</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, greedy, math, number theory</t>
+          <t>string suffix structures, strings</t>
         </is>
       </c>
       <c r="H106" s="21" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>901 ngày</t>
+          <t>854 ngày</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
@@ -28338,17 +28286,17 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>471D</t>
+          <t>1016D</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>MUH and Cube Walls</t>
+          <t>Vasya And The Matrix</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/471/D</t>
+          <t>https://codeforces.com/problemset/problem/1016/D</t>
         </is>
       </c>
       <c r="E107" s="20" t="n">
@@ -28356,22 +28304,22 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Strings</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>string suffix structures, strings</t>
+          <t>constructive algorithms, flows, math</t>
         </is>
       </c>
       <c r="H107" s="21" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>854 ngày</t>
+          <t>849 ngày</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
@@ -28391,17 +28339,17 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>1016D</t>
+          <t>1990D</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Vasya And The Matrix</t>
+          <t>Grid Puzzle</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1016/D</t>
+          <t>https://codeforces.com/problemset/problem/1990/D</t>
         </is>
       </c>
       <c r="E108" s="20" t="n">
@@ -28409,22 +28357,22 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, flows, math</t>
+          <t>bitmasks, brute force, dp, greedy, implementation</t>
         </is>
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>849 ngày</t>
+          <t>817 ngày</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -28444,17 +28392,17 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>1990D</t>
+          <t>1995C</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Grid Puzzle</t>
+          <t>Squaring</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1990/D</t>
+          <t>https://codeforces.com/problemset/problem/1995/C</t>
         </is>
       </c>
       <c r="E109" s="20" t="n">
@@ -28462,22 +28410,22 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>bitmasks, brute force, dp, greedy, implementation</t>
+          <t>brute force, constructive algorithms, greedy, implementation, math</t>
         </is>
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>817 ngày</t>
+          <t>814 ngày</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
@@ -28497,17 +28445,17 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>1995C</t>
+          <t>706D</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Squaring</t>
+          <t>Vasiliy's Multiset</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1995/C</t>
+          <t>https://codeforces.com/problemset/problem/706/D</t>
         </is>
       </c>
       <c r="E110" s="20" t="n">
@@ -28515,22 +28463,22 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>brute force, constructive algorithms, greedy, implementation, math</t>
+          <t>binary search, bitmasks, data structures, trees</t>
         </is>
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>814 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -28550,17 +28498,17 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>706D</t>
+          <t>1824B1</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Vasiliy's Multiset</t>
+          <t>LuoTianyi and the Floating Islands (Easy Version)</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/706/D</t>
+          <t>https://codeforces.com/problemset/problem/1824/B1</t>
         </is>
       </c>
       <c r="E111" s="20" t="n">
@@ -28568,12 +28516,12 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>binary search, bitmasks, data structures, trees</t>
+          <t>combinatorics, math, probabilities, trees</t>
         </is>
       </c>
       <c r="H111" s="21" t="inlineStr">
@@ -28603,17 +28551,17 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>1824B1</t>
+          <t>1856E1</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>LuoTianyi and the Floating Islands (Easy Version)</t>
+          <t>PermuTree (easy version)</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1824/B1</t>
+          <t>https://codeforces.com/problemset/problem/1856/E1</t>
         </is>
       </c>
       <c r="E112" s="20" t="n">
@@ -28621,22 +28569,22 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, math, probabilities, trees</t>
+          <t>dfs and similar, dp, trees</t>
         </is>
       </c>
       <c r="H112" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>773 ngày</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
@@ -28656,17 +28604,17 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>1856E1</t>
+          <t>2045M</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>PermuTree (easy version)</t>
+          <t>Mirror Maze</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1856/E1</t>
+          <t>https://codeforces.com/problemset/problem/2045/M</t>
         </is>
       </c>
       <c r="E113" s="20" t="n">
@@ -28679,17 +28627,17 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, dp, trees</t>
+          <t>brute force, dfs and similar, graphs, implementation</t>
         </is>
       </c>
       <c r="H113" s="21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>773 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -28709,17 +28657,17 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>2045M</t>
+          <t>2172B</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Mirror Maze</t>
+          <t>Buses</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/M</t>
+          <t>https://codeforces.com/problemset/problem/2172/B</t>
         </is>
       </c>
       <c r="E114" s="20" t="n">
@@ -28727,22 +28675,22 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs, implementation</t>
+          <t>greedy, sortings</t>
         </is>
       </c>
       <c r="H114" s="21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="I114" s="12" t="inlineStr">
-        <is>
-          <t>358 ngày</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>88 ngày</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -28762,21 +28710,21 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>2172B</t>
+          <t>1894D</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Buses</t>
+          <t>Neutral Tonality</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2172/B</t>
+          <t>https://codeforces.com/problemset/problem/1894/D</t>
         </is>
       </c>
       <c r="E115" s="20" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -28785,22 +28733,22 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>greedy, sortings</t>
+          <t>constructive algorithms, data structures, sortings, two pointers</t>
         </is>
       </c>
       <c r="H115" s="21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="I115" s="7" t="inlineStr">
-        <is>
-          <t>88 ngày</t>
-        </is>
-      </c>
-      <c r="J115" s="8" t="inlineStr">
-        <is>
-          <t>P1 - Trọng tâm ICPC/OLP (1800-1900)</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>1073 ngày</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>P3 - Luyện phản xạ nhanh (1600-1700)</t>
         </is>
       </c>
       <c r="K115" s="21" t="inlineStr">
@@ -28815,17 +28763,17 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>1894D</t>
+          <t>295B</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Neutral Tonality</t>
+          <t>Greg and Graph</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1894/D</t>
+          <t>https://codeforces.com/problemset/problem/295/B</t>
         </is>
       </c>
       <c r="E116" s="20" t="n">
@@ -28833,22 +28781,22 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>constructive algorithms, data structures, sortings, two pointers</t>
+          <t>dp, graphs, shortest paths</t>
         </is>
       </c>
       <c r="H116" s="21" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>1073 ngày</t>
+          <t>1052 ngày</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr">
@@ -28868,17 +28816,17 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>295B</t>
+          <t>697D</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Greg and Graph</t>
+          <t>Puzzles</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/295/B</t>
+          <t>https://codeforces.com/problemset/problem/697/D</t>
         </is>
       </c>
       <c r="E117" s="20" t="n">
@@ -28886,22 +28834,18 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>dp, graphs, shortest paths</t>
-        </is>
-      </c>
+          <t>General CP</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="21" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>1052 ngày</t>
+          <t>894 ngày</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr">
@@ -28921,17 +28865,17 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>697D</t>
+          <t>1975D</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Puzzles</t>
+          <t>Paint the Tree</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/697/D</t>
+          <t>https://codeforces.com/problemset/problem/1975/D</t>
         </is>
       </c>
       <c r="E118" s="20" t="n">
@@ -28939,18 +28883,22 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>General CP</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr"/>
+          <t>Graph Theory</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>brute force, dfs and similar, dp, greedy, shortest paths</t>
+        </is>
+      </c>
       <c r="H118" s="21" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>894 ngày</t>
+          <t>872 ngày</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
@@ -28970,17 +28918,17 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>1975D</t>
+          <t>126B</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Paint the Tree</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1975/D</t>
+          <t>https://codeforces.com/problemset/problem/126/B</t>
         </is>
       </c>
       <c r="E119" s="20" t="n">
@@ -28988,22 +28936,22 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, dp, greedy, shortest paths</t>
+          <t>binary search, dp, hashing, string suffix structures, strings</t>
         </is>
       </c>
       <c r="H119" s="21" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>872 ngày</t>
+          <t>854 ngày</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr">
@@ -29023,17 +28971,17 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>126B</t>
+          <t>1986E</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Beautiful Array</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/126/B</t>
+          <t>https://codeforces.com/problemset/problem/1986/E</t>
         </is>
       </c>
       <c r="E120" s="20" t="n">
@@ -29041,22 +28989,22 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>binary search, dp, hashing, string suffix structures, strings</t>
+          <t>greedy, math, number theory, sortings</t>
         </is>
       </c>
       <c r="H120" s="21" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>854 ngày</t>
+          <t>844 ngày</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr">
@@ -29076,17 +29024,17 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>1986E</t>
+          <t>1995B2</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Beautiful Array</t>
+          <t>Bouquet (Hard Version)</t>
         </is>
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1986/E</t>
+          <t>https://codeforces.com/problemset/problem/1995/B2</t>
         </is>
       </c>
       <c r="E121" s="20" t="n">
@@ -29099,17 +29047,17 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>greedy, math, number theory, sortings</t>
+          <t>binary search, data structures, greedy, math, sortings</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>844 ngày</t>
+          <t>814 ngày</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
@@ -29129,17 +29077,17 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>1995B2</t>
+          <t>1833F</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Bouquet (Hard Version)</t>
+          <t>Ira and Flamenco</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1995/B2</t>
+          <t>https://codeforces.com/problemset/problem/1833/F</t>
         </is>
       </c>
       <c r="E122" s="20" t="n">
@@ -29152,17 +29100,17 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, greedy, math, sortings</t>
+          <t>combinatorics, constructive algorithms, data structures, implementation, math</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
-          <t>814 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
@@ -29182,17 +29130,17 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>1833F</t>
+          <t>1896D</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Ira and Flamenco</t>
+          <t>Ones and Twos</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1833/F</t>
+          <t>https://codeforces.com/problemset/problem/1896/D</t>
         </is>
       </c>
       <c r="E123" s="20" t="n">
@@ -29205,7 +29153,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>combinatorics, constructive algorithms, data structures, implementation, math</t>
+          <t>binary search, data structures, divide and conquer, math, two pointers</t>
         </is>
       </c>
       <c r="H123" s="21" t="inlineStr">
@@ -29235,17 +29183,17 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>1896D</t>
+          <t>2045A</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Ones and Twos</t>
+          <t>Scrambled Scrabble</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1896/D</t>
+          <t>https://codeforces.com/problemset/problem/2045/A</t>
         </is>
       </c>
       <c r="E124" s="20" t="n">
@@ -29253,22 +29201,22 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>binary search, data structures, divide and conquer, math, two pointers</t>
+          <t>brute force, greedy</t>
         </is>
       </c>
       <c r="H124" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>358 ngày</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr">
@@ -29288,17 +29236,17 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>2045A</t>
+          <t>1906M</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Scrambled Scrabble</t>
+          <t>Triangle Construction</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2045/A</t>
+          <t>https://codeforces.com/problemset/problem/1906/M</t>
         </is>
       </c>
       <c r="E125" s="20" t="n">
@@ -29306,22 +29254,22 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>brute force, greedy</t>
+          <t>greedy, math</t>
         </is>
       </c>
       <c r="H125" s="21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>358 ngày</t>
+          <t>357 ngày</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
@@ -29341,17 +29289,17 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>1906M</t>
+          <t>2041D</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Triangle Construction</t>
+          <t>Drunken Maze</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1906/M</t>
+          <t>https://codeforces.com/problemset/problem/2041/D</t>
         </is>
       </c>
       <c r="E126" s="20" t="n">
@@ -29359,22 +29307,22 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>greedy, math</t>
+          <t>brute force, dfs and similar, graphs, shortest paths</t>
         </is>
       </c>
       <c r="H126" s="21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>357 ngày</t>
+          <t>330 ngày</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr">
@@ -29394,17 +29342,17 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>2041D</t>
+          <t>2181M</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Drunken Maze</t>
+          <t>Medical Parity</t>
         </is>
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2041/D</t>
+          <t>https://codeforces.com/problemset/problem/2181/M</t>
         </is>
       </c>
       <c r="E127" s="20" t="n">
@@ -29412,22 +29360,22 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>brute force, dfs and similar, graphs, shortest paths</t>
+          <t>dp, strings</t>
         </is>
       </c>
       <c r="H127" s="21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="I127" s="12" t="inlineStr">
-        <is>
-          <t>330 ngày</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>70 ngày</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr">
@@ -29447,40 +29395,40 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>2181M</t>
+          <t>1886C</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Medical Parity</t>
+          <t>Decreasing String</t>
         </is>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2181/M</t>
+          <t>https://codeforces.com/problemset/problem/1886/C</t>
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Strings</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>dp, strings</t>
+          <t>implementation, strings</t>
         </is>
       </c>
       <c r="H128" s="21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>70 ngày</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>1101 ngày</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr">
@@ -29500,17 +29448,17 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>1886C</t>
+          <t>1994C</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Decreasing String</t>
+          <t>Hungry Games</t>
         </is>
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1886/C</t>
+          <t>https://codeforces.com/problemset/problem/1994/C</t>
         </is>
       </c>
       <c r="E129" s="20" t="n">
@@ -29518,22 +29466,22 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Strings</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>implementation, strings</t>
+          <t>binary search, dp, two pointers</t>
         </is>
       </c>
       <c r="H129" s="21" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>1101 ngày</t>
+          <t>819 ngày</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr">
@@ -29553,17 +29501,17 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>1994C</t>
+          <t>1251C</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Hungry Games</t>
+          <t>Minimize The Integer</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1994/C</t>
+          <t>https://codeforces.com/problemset/problem/1251/C</t>
         </is>
       </c>
       <c r="E130" s="20" t="n">
@@ -29571,22 +29519,22 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>binary search, dp, two pointers</t>
+          <t>greedy, two pointers</t>
         </is>
       </c>
       <c r="H130" s="21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="I130" s="12" t="inlineStr">
         <is>
-          <t>819 ngày</t>
+          <t>800 ngày</t>
         </is>
       </c>
       <c r="J130" s="11" t="inlineStr">
@@ -29606,17 +29554,17 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>1251C</t>
+          <t>1833E</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Minimize The Integer</t>
+          <t>Round Dance</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1251/C</t>
+          <t>https://codeforces.com/problemset/problem/1833/E</t>
         </is>
       </c>
       <c r="E131" s="20" t="n">
@@ -29624,12 +29572,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>greedy, two pointers</t>
+          <t>dfs and similar, dsu, graphs, shortest paths</t>
         </is>
       </c>
       <c r="H131" s="21" t="inlineStr">
@@ -29659,17 +29607,17 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>1833E</t>
+          <t>510C</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Round Dance</t>
+          <t>Fox And Names</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1833/E</t>
+          <t>https://codeforces.com/problemset/problem/510/C</t>
         </is>
       </c>
       <c r="E132" s="20" t="n">
@@ -29682,7 +29630,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, dsu, graphs, shortest paths</t>
+          <t>dfs and similar, graphs, sortings</t>
         </is>
       </c>
       <c r="H132" s="21" t="inlineStr">
@@ -29712,17 +29660,17 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>510C</t>
+          <t>1861C</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Fox And Names</t>
+          <t>Queries for the Array</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/510/C</t>
+          <t>https://codeforces.com/problemset/problem/1861/C</t>
         </is>
       </c>
       <c r="E133" s="20" t="n">
@@ -29735,7 +29683,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>dfs and similar, graphs, sortings</t>
+          <t>data structures, dfs and similar, implementation, strings, trees</t>
         </is>
       </c>
       <c r="H133" s="21" t="inlineStr">
@@ -29765,17 +29713,17 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>1861C</t>
+          <t>2004D</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Queries for the Array</t>
+          <t>Colored Portals</t>
         </is>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/1861/C</t>
+          <t>https://codeforces.com/problemset/problem/2004/D</t>
         </is>
       </c>
       <c r="E134" s="20" t="n">
@@ -29783,22 +29731,22 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Graph Theory</t>
+          <t>Greedy &amp; Search</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>data structures, dfs and similar, implementation, strings, trees</t>
+          <t>binary search, brute force, data structures, graphs, greedy</t>
         </is>
       </c>
       <c r="H134" s="21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I134" s="12" t="inlineStr">
         <is>
-          <t>800 ngày</t>
+          <t>791 ngày</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr">
@@ -29818,17 +29766,17 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>2004D</t>
+          <t>2172F</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Colored Portals</t>
+          <t>Cluster Computing System</t>
         </is>
       </c>
       <c r="D135" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2004/D</t>
+          <t>https://codeforces.com/problemset/problem/2172/F</t>
         </is>
       </c>
       <c r="E135" s="20" t="n">
@@ -29836,22 +29784,22 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Greedy &amp; Search</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>binary search, brute force, data structures, graphs, greedy</t>
+          <t>graphs, greedy, math</t>
         </is>
       </c>
       <c r="H135" s="21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>791 ngày</t>
+          <t>332 ngày</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr">
@@ -29871,17 +29819,17 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2172F</t>
+          <t>2239B</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Cluster Computing System</t>
+          <t>Decidophobia</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2172/F</t>
+          <t>https://codeforces.com/problemset/problem/2239/B</t>
         </is>
       </c>
       <c r="E136" s="20" t="n">
@@ -29894,17 +29842,17 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>graphs, greedy, math</t>
+          <t>greedy, math, sortings, two pointers</t>
         </is>
       </c>
       <c r="H136" s="21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="I136" s="12" t="inlineStr">
-        <is>
-          <t>332 ngày</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>102 ngày</t>
         </is>
       </c>
       <c r="J136" s="11" t="inlineStr">
@@ -29924,17 +29872,17 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>2239B</t>
+          <t>2181F</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Decidophobia</t>
+          <t>Fragmented Nim</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>https://codeforces.com/problemset/problem/2239/B</t>
+          <t>https://codeforces.com/problemset/problem/2181/F</t>
         </is>
       </c>
       <c r="E137" s="20" t="n">
@@ -29942,22 +29890,22 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Game Theory &amp; Adhoc</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>greedy, math, sortings, two pointers</t>
+          <t>games</t>
         </is>
       </c>
       <c r="H137" s="21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>102 ngày</t>
+          <t>70 ngày</t>
         </is>
       </c>
       <c r="J137" s="11" t="inlineStr">
@@ -29966,59 +29914,6 @@
         </is>
       </c>
       <c r="K137" s="21" t="inlineStr">
-        <is>
-          <t>Cần Re-solve</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="19" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>2181F</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>Fragmented Nim</t>
-        </is>
-      </c>
-      <c r="D138" s="16" t="inlineStr">
-        <is>
-          <t>https://codeforces.com/problemset/problem/2181/F</t>
-        </is>
-      </c>
-      <c r="E138" s="20" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Game Theory &amp; Adhoc</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>games</t>
-        </is>
-      </c>
-      <c r="H138" s="21" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="I138" s="7" t="inlineStr">
-        <is>
-          <t>70 ngày</t>
-        </is>
-      </c>
-      <c r="J138" s="11" t="inlineStr">
-        <is>
-          <t>P3 - Luyện phản xạ nhanh (1600-1700)</t>
-        </is>
-      </c>
-      <c r="K138" s="21" t="inlineStr">
         <is>
           <t>Cần Re-solve</t>
         </is>
